--- a/YRIGOYEN 9115/Junio/YRIGOYEN-EXPENSAS-JUNIO.xlsx
+++ b/YRIGOYEN 9115/Junio/YRIGOYEN-EXPENSAS-JUNIO.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\YRIGOYEN 9115\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{015D63DE-5E7D-4B48-AA2B-94489F80CD1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D039CD5-7FD4-4E8D-843F-DF1C916ED276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilla" sheetId="1" r:id="rId1"/>
     <sheet name="Gastos" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Gastos!$A$1:$H$119</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Gastos!$A$1:$H$118</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Planilla!$A$1:$O$45</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -462,9 +462,6 @@
     <t>Redondeo</t>
   </si>
   <si>
-    <t xml:space="preserve">Sueldo encargada - Jimena Borges </t>
-  </si>
-  <si>
     <t>Aisquel Santoyo Gimenez</t>
   </si>
   <si>
@@ -520,9 +517,6 @@
   </si>
   <si>
     <t>AUMENTADOS EN abri 2025</t>
-  </si>
-  <si>
-    <t>Ingreso mal contabilizado al 7C - Ya imputado al 10C</t>
   </si>
   <si>
     <t xml:space="preserve">Nazareno e Ivon Iriarte
@@ -532,24 +526,6 @@
     <t xml:space="preserve">SRA SILVIA REEMPLAZO </t>
   </si>
   <si>
-    <t>Destapacion Italoamericana - Mantenimiento de cañerias, repaso de camaras de cloacas, salida colectora AYSA</t>
-  </si>
-  <si>
-    <t>Salvatierra Matias - Desobstruccion columna cocina 8B</t>
-  </si>
-  <si>
-    <t>Debito 07/05</t>
-  </si>
-  <si>
-    <t>Debito 12/05</t>
-  </si>
-  <si>
-    <t>Vaciamiento de guardia con bomba propia y del consorciopor ganado de agua de napa - Se asiste hasta su vaciamiento el dia 16/05 con personal - imputado a la uf PA</t>
-  </si>
-  <si>
-    <t>Punitorios mal cobrados 8C</t>
-  </si>
-  <si>
     <t>Daniel Salgueiro</t>
   </si>
   <si>
@@ -565,19 +541,43 @@
     <t>MES DE JUNIO</t>
   </si>
   <si>
-    <t xml:space="preserve">Casa monini </t>
-  </si>
-  <si>
     <t xml:space="preserve">Servisur 12/06 - Reconeccion circuito pulsadores y reemplazo de 6 de los mismos </t>
   </si>
   <si>
-    <t>Impermeabilizacion interna tanque de reserva compartimiento cambio de dos tapas y marcos laterales - Limpieza y desinfeccion de tanques de agua potable - Anticipo cuota 2 de 4</t>
-  </si>
-  <si>
-    <t>Articulos de limpieza</t>
-  </si>
-  <si>
     <t>Fumigacion Lanus 09/06</t>
+  </si>
+  <si>
+    <t>Debito 09/06</t>
+  </si>
+  <si>
+    <t>Debito 13/06</t>
+  </si>
+  <si>
+    <t>Impermeabilizacion interna tanque de reserva compartimiento cambio de dos tapas y marcos laterales - Limpieza y desinfeccion de tanques de agua potable -  cuota 2 de 4</t>
+  </si>
+  <si>
+    <t>Casa monini - Compra de pulsadores y compra de teclas de luz</t>
+  </si>
+  <si>
+    <t>Antonio Santillan - Gasista matriculado - Transferencia 02/06 y 05/06 - Arreglo perdida de gas 9A</t>
+  </si>
+  <si>
+    <t>Imputacion de gasto incorrecta - Mes anterior - Destapacion Italoamericana - Mantenimiento de cañerias, repaso de camaras de cloacas, salida colectora AYSA</t>
+  </si>
+  <si>
+    <t>Articulos de limpieza - Transf 11/06</t>
+  </si>
+  <si>
+    <t>Sueldo encargada - Jimena Borges y SAC</t>
+  </si>
+  <si>
+    <t>Servisur 27/05 - Reemplazo de tres lamparas en pasillos y en el 10A - Material y mano de obra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urbeco - Cambio de tapa y marco de tanques cisternas de vombeo </t>
+  </si>
+  <si>
+    <t>macarena en febrero no le contamos un pago de 109277 , por lo que viene arrastrando una deuda inexistente, hay que corregirlo</t>
   </si>
 </sst>
 </file>
@@ -825,7 +825,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -880,6 +880,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="43">
     <border>
@@ -1405,7 +1411,7 @@
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="240">
+  <cellXfs count="238">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1675,6 +1681,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1705,6 +1720,15 @@
     <xf numFmtId="166" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1741,17 +1765,8 @@
     <xf numFmtId="0" fontId="30" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1774,10 +1789,10 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1870,26 +1885,11 @@
     <xf numFmtId="0" fontId="29" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="10" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2306,7 +2306,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:P45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.5703125" customWidth="1"/>
@@ -2374,13 +2374,13 @@
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
-      <c r="F3" s="167" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3" s="168"/>
-      <c r="H3" s="168"/>
-      <c r="I3" s="168"/>
-      <c r="J3" s="169"/>
+      <c r="F3" s="170" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3" s="171"/>
+      <c r="H3" s="171"/>
+      <c r="I3" s="171"/>
+      <c r="J3" s="172"/>
       <c r="K3" s="147"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
@@ -2395,11 +2395,11 @@
       <c r="C4" s="6"/>
       <c r="D4" s="8"/>
       <c r="E4" s="145"/>
-      <c r="F4" s="170"/>
-      <c r="G4" s="171"/>
-      <c r="H4" s="171"/>
-      <c r="I4" s="171"/>
-      <c r="J4" s="172"/>
+      <c r="F4" s="173"/>
+      <c r="G4" s="174"/>
+      <c r="H4" s="174"/>
+      <c r="I4" s="174"/>
+      <c r="J4" s="175"/>
       <c r="K4" s="147"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
@@ -2408,20 +2408,20 @@
     </row>
     <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15"/>
-      <c r="B5" s="176">
+      <c r="B5" s="179">
         <f>C3</f>
         <v>5000000</v>
       </c>
-      <c r="C5" s="176"/>
+      <c r="C5" s="179"/>
       <c r="D5" s="16"/>
       <c r="E5" s="146">
         <v>0</v>
       </c>
-      <c r="F5" s="170"/>
-      <c r="G5" s="171"/>
-      <c r="H5" s="171"/>
-      <c r="I5" s="171"/>
-      <c r="J5" s="172"/>
+      <c r="F5" s="173"/>
+      <c r="G5" s="174"/>
+      <c r="H5" s="174"/>
+      <c r="I5" s="174"/>
+      <c r="J5" s="175"/>
       <c r="K5" s="148"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
@@ -2436,11 +2436,11 @@
       <c r="C6" s="18"/>
       <c r="D6" s="16"/>
       <c r="E6" s="145"/>
-      <c r="F6" s="173"/>
-      <c r="G6" s="174"/>
-      <c r="H6" s="174"/>
-      <c r="I6" s="174"/>
-      <c r="J6" s="175"/>
+      <c r="F6" s="176"/>
+      <c r="G6" s="177"/>
+      <c r="H6" s="177"/>
+      <c r="I6" s="177"/>
+      <c r="J6" s="178"/>
       <c r="K6" s="148"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
@@ -2449,11 +2449,11 @@
     </row>
     <row r="7" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15"/>
-      <c r="B7" s="176">
+      <c r="B7" s="179">
         <f>C2</f>
         <v>0</v>
       </c>
-      <c r="C7" s="176"/>
+      <c r="C7" s="179"/>
       <c r="D7" s="16"/>
       <c r="E7" s="18"/>
       <c r="F7" s="32"/>
@@ -2499,7 +2499,7 @@
         <v>12</v>
       </c>
       <c r="K8" s="23" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L8" s="20" t="s">
         <v>13</v>
@@ -2529,11 +2529,11 @@
         <v>0.108</v>
       </c>
       <c r="F9" s="31">
-        <v>534000.05020000006</v>
+        <v>540000</v>
       </c>
       <c r="G9" s="150">
         <f>F9</f>
-        <v>534000.05020000006</v>
+        <v>540000</v>
       </c>
       <c r="H9" s="32">
         <f t="shared" ref="H9:H42" si="0">IF(F9&gt;G9,F9-G9,0)</f>
@@ -2631,10 +2631,10 @@
         <v>2.5600000000000001E-2</v>
       </c>
       <c r="F11" s="31">
-        <v>127999.54967758546</v>
+        <v>127948.34067113716</v>
       </c>
       <c r="G11" s="151">
-        <v>130560</v>
+        <v>128000</v>
       </c>
       <c r="H11" s="32">
         <f t="shared" si="0"/>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="J11" s="32">
         <f t="shared" si="2"/>
-        <v>2560.4503224145446</v>
+        <v>51.659328862835537</v>
       </c>
       <c r="K11" s="32"/>
       <c r="L11" s="33">
@@ -2659,11 +2659,11 @@
       </c>
       <c r="N11" s="34">
         <f>H11+I11-J11+K11+L11+M11+E7</f>
-        <v>125439.54967758546</v>
+        <v>127948.34067113716</v>
       </c>
       <c r="O11" s="35">
         <f t="shared" si="6"/>
-        <v>127948.34067113716</v>
+        <v>130507.3074845599</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2735,11 +2735,11 @@
         <v>1.7299999999999999E-2</v>
       </c>
       <c r="F13" s="31">
-        <v>86500</v>
+        <v>88230</v>
       </c>
       <c r="G13" s="151">
         <f>F13</f>
-        <v>86500</v>
+        <v>88230</v>
       </c>
       <c r="H13" s="32">
         <f t="shared" si="0"/>
@@ -2786,10 +2786,10 @@
         <v>2.7900000000000001E-2</v>
       </c>
       <c r="F14" s="31">
-        <v>139366.92475261347</v>
+        <v>138866.92475261347</v>
       </c>
       <c r="G14" s="151">
-        <v>140000</v>
+        <v>139000</v>
       </c>
       <c r="H14" s="32">
         <f t="shared" si="0"/>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="J14" s="32">
         <f t="shared" si="2"/>
-        <v>633.07524738652864</v>
+        <v>133.07524738652864</v>
       </c>
       <c r="K14" s="32"/>
       <c r="L14" s="33">
@@ -2814,11 +2814,11 @@
       </c>
       <c r="N14" s="34">
         <f t="shared" si="5"/>
-        <v>138866.92475261347</v>
+        <v>139366.92475261347</v>
       </c>
       <c r="O14" s="35">
         <f t="shared" si="6"/>
-        <v>141644.26324766575</v>
+        <v>142154.26324766575</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2883,17 +2883,17 @@
         <v>32</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E16" s="30">
         <v>2.1499999999999998E-2</v>
       </c>
       <c r="F16" s="31">
-        <v>105256.07647499999</v>
+        <v>107499.99999999999</v>
       </c>
       <c r="G16" s="151">
         <f>F16</f>
-        <v>105256.07647499999</v>
+        <v>107499.99999999999</v>
       </c>
       <c r="H16" s="32">
         <f t="shared" si="0"/>
@@ -2942,16 +2942,18 @@
         <v>1.3599999999999999E-2</v>
       </c>
       <c r="F17" s="31">
-        <v>213948.80753304131</v>
-      </c>
-      <c r="G17" s="151"/>
+        <v>288367.27175903256</v>
+      </c>
+      <c r="G17" s="151">
+        <v>100000</v>
+      </c>
       <c r="H17" s="32">
         <f t="shared" si="0"/>
-        <v>213948.80753304131</v>
+        <v>188367.27175903256</v>
       </c>
       <c r="I17" s="32">
         <f t="shared" si="1"/>
-        <v>6418.4642259912389</v>
+        <v>5651.0181527709765</v>
       </c>
       <c r="J17" s="32">
         <f t="shared" si="2"/>
@@ -2968,11 +2970,11 @@
       </c>
       <c r="N17" s="34">
         <f t="shared" si="5"/>
-        <v>288367.27175903256</v>
+        <v>262018.28991180353</v>
       </c>
       <c r="O17" s="35">
         <f t="shared" si="6"/>
-        <v>294134.61719421321</v>
+        <v>267258.6557100396</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2986,7 +2988,7 @@
         <v>134</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E18" s="30">
         <v>2.7900000000000001E-2</v>
@@ -3039,7 +3041,7 @@
         <v>37</v>
       </c>
       <c r="D19" s="166" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E19" s="30">
         <v>2.4899999999999999E-2</v>
@@ -3096,23 +3098,22 @@
         <v>3.6700000000000003E-2</v>
       </c>
       <c r="F20" s="31">
-        <v>380762.08600565005</v>
+        <v>167547.32772576308</v>
       </c>
       <c r="G20" s="151">
-        <f>400000</f>
-        <v>400000</v>
+        <v>165000</v>
       </c>
       <c r="H20" s="32">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2547.3277257630834</v>
       </c>
       <c r="I20" s="32">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>76.419831772892493</v>
       </c>
       <c r="J20" s="32">
         <f t="shared" si="2"/>
-        <v>19237.913994349947</v>
+        <v>0</v>
       </c>
       <c r="K20" s="32"/>
       <c r="L20" s="33">
@@ -3125,11 +3126,11 @@
       </c>
       <c r="N20" s="34">
         <f t="shared" si="5"/>
-        <v>164262.08600565008</v>
+        <v>186123.747557536</v>
       </c>
       <c r="O20" s="35">
         <f t="shared" si="6"/>
-        <v>167547.32772576308</v>
+        <v>189846.22250868671</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3149,10 +3150,11 @@
         <v>2.7900000000000001E-2</v>
       </c>
       <c r="F21" s="31">
-        <v>139500</v>
+        <v>136710</v>
       </c>
       <c r="G21" s="151">
-        <v>142290</v>
+        <f>F21</f>
+        <v>136710</v>
       </c>
       <c r="H21" s="32">
         <f t="shared" si="0"/>
@@ -3164,7 +3166,7 @@
       </c>
       <c r="J21" s="32">
         <f t="shared" si="2"/>
-        <v>2790</v>
+        <v>0</v>
       </c>
       <c r="K21" s="32"/>
       <c r="L21" s="33">
@@ -3177,11 +3179,11 @@
       </c>
       <c r="N21" s="34">
         <f t="shared" si="5"/>
-        <v>136710</v>
+        <v>139500</v>
       </c>
       <c r="O21" s="35">
         <f t="shared" si="6"/>
-        <v>139444.20000000001</v>
+        <v>142290</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3246,7 +3248,7 @@
         <v>45</v>
       </c>
       <c r="D23" s="47" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E23" s="30">
         <v>3.6700000000000003E-2</v>
@@ -3299,24 +3301,24 @@
         <v>47</v>
       </c>
       <c r="D24" s="50" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E24" s="30">
         <v>2.7900000000000001E-2</v>
       </c>
       <c r="F24" s="31">
-        <v>228323.19719321662</v>
+        <v>230987.89310901312</v>
       </c>
       <c r="G24" s="151">
         <v>139500</v>
       </c>
       <c r="H24" s="32">
         <f t="shared" si="0"/>
-        <v>88823.19719321662</v>
+        <v>91487.893109013123</v>
       </c>
       <c r="I24" s="32">
         <f t="shared" si="1"/>
-        <v>2664.6959157964984</v>
+        <v>2744.6367932703934</v>
       </c>
       <c r="J24" s="32">
         <f t="shared" si="2"/>
@@ -3333,11 +3335,11 @@
       </c>
       <c r="N24" s="34">
         <f t="shared" si="5"/>
-        <v>230987.89310901312</v>
+        <v>233732.52990228351</v>
       </c>
       <c r="O24" s="35">
         <f t="shared" si="6"/>
-        <v>235607.65097119339</v>
+        <v>238407.18050032918</v>
       </c>
     </row>
     <row r="25" spans="1:15" s="52" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3355,10 +3357,11 @@
         <v>2.4899999999999999E-2</v>
       </c>
       <c r="F25" s="31">
-        <v>121956.77512699999</v>
+        <v>122060.77512699997</v>
       </c>
       <c r="G25" s="151">
-        <v>124396</v>
+        <f>122061</f>
+        <v>122061</v>
       </c>
       <c r="H25" s="32">
         <f t="shared" si="0"/>
@@ -3370,7 +3373,7 @@
       </c>
       <c r="J25" s="32">
         <f t="shared" si="2"/>
-        <v>2439.2248730000138</v>
+        <v>0.22487300002831034</v>
       </c>
       <c r="K25" s="32"/>
       <c r="L25" s="33">
@@ -3383,11 +3386,11 @@
       </c>
       <c r="N25" s="34">
         <f t="shared" si="5"/>
-        <v>122060.77512699997</v>
+        <v>124499.77512699996</v>
       </c>
       <c r="O25" s="35">
         <f t="shared" si="6"/>
-        <v>124501.99062953997</v>
+        <v>126989.77062953995</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3405,10 +3408,11 @@
         <v>3.6700000000000003E-2</v>
       </c>
       <c r="F26" s="31">
-        <v>183016.58835500004</v>
+        <v>179516.58835500007</v>
       </c>
       <c r="G26" s="151">
-        <v>187000</v>
+        <f>F26</f>
+        <v>179516.58835500007</v>
       </c>
       <c r="H26" s="32">
         <f t="shared" si="0"/>
@@ -3420,7 +3424,7 @@
       </c>
       <c r="J26" s="32">
         <f t="shared" si="2"/>
-        <v>3983.4116449999565</v>
+        <v>0</v>
       </c>
       <c r="K26" s="32"/>
       <c r="L26" s="33">
@@ -3433,11 +3437,11 @@
       </c>
       <c r="N26" s="34">
         <f t="shared" si="5"/>
-        <v>179516.58835500007</v>
+        <v>183500.00000000003</v>
       </c>
       <c r="O26" s="35">
         <f t="shared" si="6"/>
-        <v>183106.92012210007</v>
+        <v>187170.00000000003</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3506,22 +3510,20 @@
         <v>2.4899999999999999E-2</v>
       </c>
       <c r="F28" s="31">
-        <v>258336.61747973313</v>
-      </c>
-      <c r="G28" s="151">
-        <v>263503</v>
-      </c>
+        <v>119333.61747973312</v>
+      </c>
+      <c r="G28" s="151"/>
       <c r="H28" s="54">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>119333.61747973312</v>
       </c>
       <c r="I28" s="32">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3580.0085243919934</v>
       </c>
       <c r="J28" s="32">
         <f t="shared" si="2"/>
-        <v>5166.3825202668668</v>
+        <v>0</v>
       </c>
       <c r="K28" s="32"/>
       <c r="L28" s="33">
@@ -3534,11 +3536,11 @@
       </c>
       <c r="N28" s="34">
         <f t="shared" si="5"/>
-        <v>119333.61747973312</v>
+        <v>247413.62600412511</v>
       </c>
       <c r="O28" s="35">
         <f t="shared" si="6"/>
-        <v>121720.28982932778</v>
+        <v>252361.89852420762</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3552,16 +3554,17 @@
         <v>57</v>
       </c>
       <c r="D29" s="50" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E29" s="30">
         <v>3.6700000000000003E-2</v>
       </c>
       <c r="F29" s="31">
-        <v>183500.00000000003</v>
+        <v>179000.00000000006</v>
       </c>
       <c r="G29" s="151">
-        <v>188000</v>
+        <f>F29</f>
+        <v>179000.00000000006</v>
       </c>
       <c r="H29" s="32">
         <f t="shared" si="0"/>
@@ -3573,7 +3576,7 @@
       </c>
       <c r="J29" s="32">
         <f t="shared" si="2"/>
-        <v>4499.9999999999709</v>
+        <v>0</v>
       </c>
       <c r="K29" s="32"/>
       <c r="L29" s="33">
@@ -3586,11 +3589,11 @@
       </c>
       <c r="N29" s="34">
         <f t="shared" si="5"/>
-        <v>179000.00000000006</v>
+        <v>183500.00000000003</v>
       </c>
       <c r="O29" s="35">
         <f t="shared" si="6"/>
-        <v>182580.00000000006</v>
+        <v>187170.00000000003</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3661,16 +3664,16 @@
         <v>2.4899999999999999E-2</v>
       </c>
       <c r="F31" s="31">
-        <v>258337.19954083255</v>
+        <v>390587.31552705751</v>
       </c>
       <c r="G31" s="151"/>
       <c r="H31" s="32">
         <f t="shared" si="0"/>
-        <v>258337.19954083255</v>
+        <v>390587.31552705751</v>
       </c>
       <c r="I31" s="32">
         <f t="shared" si="1"/>
-        <v>7750.115986224976</v>
+        <v>11717.619465811726</v>
       </c>
       <c r="J31" s="32">
         <f t="shared" si="2"/>
@@ -3687,11 +3690,11 @@
       </c>
       <c r="N31" s="34">
         <f t="shared" si="5"/>
-        <v>390587.31552705751</v>
+        <v>526804.93499286915</v>
       </c>
       <c r="O31" s="35">
         <f t="shared" si="6"/>
-        <v>398399.06183759868</v>
+        <v>537341.03369272652</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
@@ -3705,25 +3708,22 @@
         <v>64</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E32" s="30">
         <v>3.6700000000000003E-2</v>
       </c>
       <c r="F32" s="18">
-        <v>509914.95410339313</v>
-      </c>
-      <c r="G32" s="151">
-        <f>43566+183500</f>
-        <v>227066</v>
-      </c>
+        <v>474834.42272649496</v>
+      </c>
+      <c r="G32" s="151"/>
       <c r="H32" s="32">
         <f t="shared" si="0"/>
-        <v>282848.95410339313</v>
+        <v>474834.42272649496</v>
       </c>
       <c r="I32" s="32">
         <f t="shared" si="1"/>
-        <v>8485.4686231017931</v>
+        <v>14245.032681794848</v>
       </c>
       <c r="J32" s="32">
         <f t="shared" si="2"/>
@@ -3740,11 +3740,11 @@
       </c>
       <c r="N32" s="34">
         <f t="shared" si="5"/>
-        <v>474834.42272649496</v>
+        <v>672579.4554082898</v>
       </c>
       <c r="O32" s="35">
         <f t="shared" si="6"/>
-        <v>484331.11118102487</v>
+        <v>686031.04451645561</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -3764,11 +3764,11 @@
       <c r="E33" s="30">
         <v>2.7900000000000001E-2</v>
       </c>
-      <c r="F33" s="122">
-        <v>436113.03864328715</v>
+      <c r="F33" s="127">
+        <v>130777.73864328716</v>
       </c>
       <c r="G33" s="151">
-        <v>444835.3</v>
+        <v>135000</v>
       </c>
       <c r="H33" s="32">
         <f t="shared" si="0"/>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="J33" s="32">
         <f t="shared" si="2"/>
-        <v>8722.2613567128428</v>
+        <v>4222.2613567128428</v>
       </c>
       <c r="K33" s="9"/>
       <c r="L33" s="33">
@@ -3793,11 +3793,11 @@
       </c>
       <c r="N33" s="34">
         <f t="shared" si="5"/>
-        <v>130777.73864328716</v>
+        <v>135277.73864328716</v>
       </c>
       <c r="O33" s="35">
         <f t="shared" si="6"/>
-        <v>133393.29341615291</v>
+        <v>137983.29341615291</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -3870,19 +3870,19 @@
         <v>3.6700000000000003E-2</v>
       </c>
       <c r="F35" s="18">
-        <v>380762.08600565005</v>
+        <v>183500.08858581958</v>
       </c>
       <c r="G35" s="151">
-        <f>197262+183500</f>
-        <v>380762</v>
+        <f>F35</f>
+        <v>183500.08858581958</v>
       </c>
       <c r="H35" s="32">
         <f t="shared" si="0"/>
-        <v>8.6005650053266436E-2</v>
+        <v>0</v>
       </c>
       <c r="I35" s="32">
         <f t="shared" si="1"/>
-        <v>2.580169501597993E-3</v>
+        <v>0</v>
       </c>
       <c r="J35" s="32">
         <f t="shared" si="2"/>
@@ -3899,11 +3899,11 @@
       </c>
       <c r="N35" s="34">
         <f t="shared" si="5"/>
-        <v>183500.08858581958</v>
+        <v>183500.00000000003</v>
       </c>
       <c r="O35" s="35">
         <f t="shared" si="6"/>
-        <v>187170.09035753598</v>
+        <v>187170.00000000003</v>
       </c>
       <c r="P35" s="87"/>
     </row>
@@ -3973,7 +3973,7 @@
         <v>76</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E37" s="30">
         <v>2.4899999999999999E-2</v>
@@ -4027,24 +4027,24 @@
         <v>78</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="E38" s="30">
         <v>2.1499999999999998E-2</v>
       </c>
       <c r="F38" s="18">
-        <v>337765.75706475682</v>
-      </c>
-      <c r="G38" s="151">
+        <v>344673.7297766995</v>
+      </c>
+      <c r="G38" s="236">
         <v>107500</v>
       </c>
       <c r="H38" s="32">
         <f t="shared" si="0"/>
-        <v>230265.75706475682</v>
+        <v>237173.7297766995</v>
       </c>
       <c r="I38" s="32">
         <f t="shared" si="1"/>
-        <v>6907.9727119427043</v>
+        <v>7115.2118933009851</v>
       </c>
       <c r="J38" s="32">
         <f t="shared" si="2"/>
@@ -4061,11 +4061,11 @@
       </c>
       <c r="N38" s="34">
         <f t="shared" si="5"/>
-        <v>344673.7297766995</v>
+        <v>351788.94167000049</v>
       </c>
       <c r="O38" s="35">
         <f t="shared" si="6"/>
-        <v>351567.20437223348</v>
+        <v>358824.72050340049</v>
       </c>
     </row>
     <row r="39" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -4246,19 +4246,19 @@
         <v>3.6700000000000003E-2</v>
       </c>
       <c r="F42" s="60">
-        <v>296934.42345230939</v>
+        <v>183500.43615587871</v>
       </c>
       <c r="G42" s="152">
-        <f>155000+185500-43566</f>
-        <v>296934</v>
+        <f>F42</f>
+        <v>183500.43615587871</v>
       </c>
       <c r="H42" s="32">
         <f t="shared" si="0"/>
-        <v>0.42345230939099565</v>
+        <v>0</v>
       </c>
       <c r="I42" s="32">
         <f t="shared" si="1"/>
-        <v>1.2703569281729868E-2</v>
+        <v>0</v>
       </c>
       <c r="J42" s="32">
         <f t="shared" si="2"/>
@@ -4275,11 +4275,11 @@
       </c>
       <c r="N42" s="34">
         <f t="shared" si="5"/>
-        <v>183500.43615587871</v>
+        <v>183500.00000000003</v>
       </c>
       <c r="O42" s="35">
         <f t="shared" si="6"/>
-        <v>187170.44487899629</v>
+        <v>187170.00000000003</v>
       </c>
     </row>
     <row r="43" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4293,23 +4293,23 @@
       </c>
       <c r="F43" s="65">
         <f>SUM(F9:F42)</f>
-        <v>6869794.1316090701</v>
+        <v>6081442.4703945303</v>
       </c>
       <c r="G43" s="144">
         <f t="shared" ref="G43:N43" si="9">SUM(G9:G42)</f>
-        <v>5845602.4266750002</v>
+        <v>4581518.1130966982</v>
       </c>
       <c r="H43" s="66">
         <f t="shared" si="9"/>
-        <v>1074224.4248931999</v>
+        <v>1504331.578103794</v>
       </c>
       <c r="I43" s="67">
         <f t="shared" si="9"/>
-        <v>32226.732746795995</v>
+        <v>45129.94734311381</v>
       </c>
       <c r="J43" s="68">
         <f t="shared" si="9"/>
-        <v>50032.719959130671</v>
+        <v>4407.2208059622353</v>
       </c>
       <c r="K43" s="130">
         <f t="shared" si="9"/>
@@ -4325,10 +4325,15 @@
       </c>
       <c r="N43" s="65">
         <f t="shared" si="9"/>
-        <v>6073918.4376808656</v>
+        <v>6562554.304640945</v>
       </c>
       <c r="O43" s="65"/>
       <c r="P43" s="69"/>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G45" s="237" t="s">
+        <v>182</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4344,7 +4349,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K117"/>
+  <dimension ref="A1:K116"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -4370,23 +4375,23 @@
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="38"/>
-      <c r="D2" s="219"/>
-      <c r="E2" s="220"/>
-      <c r="F2" s="220"/>
-      <c r="G2" s="220"/>
-      <c r="H2" s="221"/>
+      <c r="D2" s="222"/>
+      <c r="E2" s="223"/>
+      <c r="F2" s="223"/>
+      <c r="G2" s="223"/>
+      <c r="H2" s="224"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="38"/>
       <c r="D3" s="74" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="222" t="s">
+      <c r="E3" s="225" t="s">
         <v>89</v>
       </c>
-      <c r="F3" s="222"/>
-      <c r="G3" s="222"/>
-      <c r="H3" s="223"/>
+      <c r="F3" s="225"/>
+      <c r="G3" s="225"/>
+      <c r="H3" s="226"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="38"/>
@@ -4431,13 +4436,13 @@
       </c>
       <c r="B8" s="79"/>
       <c r="C8" s="79" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="D8" s="79"/>
       <c r="E8" s="79"/>
       <c r="F8" s="80"/>
       <c r="G8" s="79" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="H8" s="81"/>
     </row>
@@ -4454,16 +4459,16 @@
       <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="224" t="s">
+      <c r="A10" s="227" t="s">
         <v>98</v>
       </c>
-      <c r="B10" s="225"/>
-      <c r="C10" s="225"/>
-      <c r="D10" s="225"/>
-      <c r="E10" s="225"/>
-      <c r="F10" s="225"/>
-      <c r="G10" s="225"/>
-      <c r="H10" s="226"/>
+      <c r="B10" s="228"/>
+      <c r="C10" s="228"/>
+      <c r="D10" s="228"/>
+      <c r="E10" s="228"/>
+      <c r="F10" s="228"/>
+      <c r="G10" s="228"/>
+      <c r="H10" s="229"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="14"/>
@@ -4476,20 +4481,20 @@
       <c r="H11" s="6"/>
     </row>
     <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="227" t="s">
+      <c r="A12" s="230" t="s">
         <v>99</v>
       </c>
-      <c r="B12" s="227"/>
-      <c r="C12" s="227"/>
-      <c r="D12" s="227"/>
-      <c r="E12" s="227"/>
-      <c r="F12" s="227"/>
-      <c r="G12" s="227"/>
-      <c r="H12" s="227"/>
+      <c r="B12" s="230"/>
+      <c r="C12" s="230"/>
+      <c r="D12" s="230"/>
+      <c r="E12" s="230"/>
+      <c r="F12" s="230"/>
+      <c r="G12" s="230"/>
+      <c r="H12" s="230"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="153" t="s">
-        <v>144</v>
+        <v>179</v>
       </c>
       <c r="B13" s="154"/>
       <c r="C13" s="154"/>
@@ -4498,7 +4503,7 @@
       <c r="F13" s="154"/>
       <c r="G13" s="154"/>
       <c r="H13" s="82">
-        <v>1078821.3899999999</v>
+        <v>1552501</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -4512,7 +4517,7 @@
       <c r="F14" s="154"/>
       <c r="G14" s="154"/>
       <c r="H14" s="82">
-        <v>0.25</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -4526,10 +4531,11 @@
       <c r="F15" s="155"/>
       <c r="G15" s="155"/>
       <c r="H15" s="82">
-        <v>-234643.64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+        <f>-337668.97</f>
+        <v>-337668.97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="156" t="s">
         <v>100</v>
       </c>
@@ -4541,25 +4547,25 @@
       <c r="G16" s="157"/>
       <c r="H16" s="84">
         <f>SUM(H13:H15)</f>
-        <v>844177.99999999988</v>
+        <v>1214833</v>
       </c>
       <c r="I16" s="83"/>
     </row>
-    <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="228" t="s">
-        <v>166</v>
-      </c>
-      <c r="B17" s="228"/>
-      <c r="C17" s="228"/>
-      <c r="D17" s="228"/>
-      <c r="E17" s="228"/>
-      <c r="F17" s="228"/>
-      <c r="G17" s="228"/>
-      <c r="H17" s="228"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="231" t="s">
+        <v>164</v>
+      </c>
+      <c r="B17" s="231"/>
+      <c r="C17" s="231"/>
+      <c r="D17" s="231"/>
+      <c r="E17" s="231"/>
+      <c r="F17" s="231"/>
+      <c r="G17" s="231"/>
+      <c r="H17" s="231"/>
+    </row>
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="85" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B18" s="154"/>
       <c r="C18" s="154"/>
@@ -4567,13 +4573,11 @@
       <c r="E18" s="154"/>
       <c r="F18" s="154"/>
       <c r="G18" s="154"/>
-      <c r="H18" s="82">
-        <v>47000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H18" s="82"/>
+    </row>
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="85" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B19" s="154"/>
       <c r="C19" s="154"/>
@@ -4581,11 +4585,9 @@
       <c r="E19" s="154"/>
       <c r="F19" s="154"/>
       <c r="G19" s="154"/>
-      <c r="H19" s="82">
-        <v>3567.21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H19" s="82"/>
+    </row>
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="154"/>
       <c r="B20" s="154"/>
       <c r="C20" s="154"/>
@@ -4595,7 +4597,7 @@
       <c r="G20" s="154"/>
       <c r="H20" s="82"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="154" t="s">
         <v>102</v>
       </c>
@@ -4607,51 +4609,51 @@
       <c r="G21" s="154"/>
       <c r="H21" s="82">
         <f>SUM(H18:H20)</f>
-        <v>50567.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="228" t="s">
+      <c r="A22" s="231" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="228"/>
-      <c r="C22" s="228"/>
-      <c r="D22" s="228"/>
-      <c r="E22" s="228"/>
-      <c r="F22" s="228"/>
-      <c r="G22" s="228"/>
-      <c r="H22" s="228"/>
+      <c r="B22" s="231"/>
+      <c r="C22" s="231"/>
+      <c r="D22" s="231"/>
+      <c r="E22" s="231"/>
+      <c r="F22" s="231"/>
+      <c r="G22" s="231"/>
+      <c r="H22" s="231"/>
     </row>
     <row r="23" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="153" t="s">
         <v>104</v>
       </c>
       <c r="B23" s="158" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C23" s="158"/>
       <c r="D23" s="158"/>
       <c r="E23" s="158"/>
       <c r="F23" s="158"/>
       <c r="G23" s="154"/>
-      <c r="H23" s="238">
+      <c r="H23" s="82">
         <v>94123.39</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="153" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B24" s="154" t="str">
         <f>B23</f>
-        <v>Debito 12/05</v>
+        <v>Debito 13/06</v>
       </c>
       <c r="C24" s="158"/>
       <c r="D24" s="158"/>
       <c r="E24" s="158"/>
       <c r="F24" s="158"/>
       <c r="G24" s="154"/>
-      <c r="H24" s="238">
+      <c r="H24" s="82">
         <v>48546.96</v>
       </c>
     </row>
@@ -4661,30 +4663,30 @@
       </c>
       <c r="B25" s="154" t="str">
         <f>B24</f>
-        <v>Debito 12/05</v>
+        <v>Debito 13/06</v>
       </c>
       <c r="C25" s="158"/>
       <c r="D25" s="158"/>
       <c r="E25" s="158"/>
       <c r="F25" s="158"/>
       <c r="G25" s="154"/>
-      <c r="H25" s="238">
+      <c r="H25" s="82">
         <v>5394.11</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="153" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B26" s="154" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C26" s="158"/>
       <c r="D26" s="158"/>
       <c r="E26" s="158"/>
       <c r="F26" s="158"/>
       <c r="G26" s="154"/>
-      <c r="H26" s="238">
+      <c r="H26" s="82">
         <v>496397.21</v>
       </c>
     </row>
@@ -4716,16 +4718,16 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="218" t="s">
+      <c r="A29" s="221" t="s">
         <v>107</v>
       </c>
-      <c r="B29" s="218"/>
-      <c r="C29" s="218"/>
-      <c r="D29" s="218"/>
-      <c r="E29" s="218"/>
-      <c r="F29" s="218"/>
-      <c r="G29" s="218"/>
-      <c r="H29" s="218"/>
+      <c r="B29" s="221"/>
+      <c r="C29" s="221"/>
+      <c r="D29" s="221"/>
+      <c r="E29" s="221"/>
+      <c r="F29" s="221"/>
+      <c r="G29" s="221"/>
+      <c r="H29" s="221"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="154" t="s">
@@ -4737,7 +4739,7 @@
       <c r="E30" s="154"/>
       <c r="F30" s="154"/>
       <c r="G30" s="154"/>
-      <c r="H30" s="238">
+      <c r="H30" s="82">
         <v>4128.4799999999996</v>
       </c>
     </row>
@@ -4754,7 +4756,7 @@
       <c r="F31" s="154"/>
       <c r="G31" s="154"/>
       <c r="H31" s="82">
-        <v>1229017.1299999999</v>
+        <v>1229017.1599999999</v>
       </c>
       <c r="I31" s="87"/>
     </row>
@@ -4770,8 +4772,8 @@
       <c r="E32" s="154"/>
       <c r="F32" s="154"/>
       <c r="G32" s="154"/>
-      <c r="H32" s="238">
-        <v>190478.54</v>
+      <c r="H32" s="82">
+        <v>189273</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -4786,20 +4788,20 @@
       <c r="G33" s="157"/>
       <c r="H33" s="160">
         <f>SUM(H30:H32)</f>
-        <v>1423624.15</v>
+        <v>1422418.64</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="218" t="s">
+      <c r="A34" s="221" t="s">
         <v>113</v>
       </c>
-      <c r="B34" s="218"/>
-      <c r="C34" s="218"/>
-      <c r="D34" s="218"/>
-      <c r="E34" s="218"/>
-      <c r="F34" s="218"/>
-      <c r="G34" s="218"/>
-      <c r="H34" s="218"/>
+      <c r="B34" s="221"/>
+      <c r="C34" s="221"/>
+      <c r="D34" s="221"/>
+      <c r="E34" s="221"/>
+      <c r="F34" s="221"/>
+      <c r="G34" s="221"/>
+      <c r="H34" s="221"/>
     </row>
     <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="85"/>
@@ -4813,7 +4815,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="85" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B36" s="161"/>
       <c r="C36" s="154"/>
@@ -4821,13 +4823,13 @@
       <c r="E36" s="154"/>
       <c r="F36" s="154"/>
       <c r="G36" s="154"/>
-      <c r="H36" s="238">
+      <c r="H36" s="82">
         <v>140000</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="85" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="B37" s="162"/>
       <c r="C37" s="85"/>
@@ -4835,29 +4837,28 @@
       <c r="E37" s="85"/>
       <c r="F37" s="85"/>
       <c r="G37" s="85"/>
-      <c r="H37" s="238">
+      <c r="H37" s="82">
         <v>40000</v>
       </c>
       <c r="J37" s="87"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="85" t="s">
-        <v>168</v>
-      </c>
-      <c r="B38" s="162"/>
-      <c r="C38" s="85"/>
-      <c r="D38" s="85"/>
-      <c r="E38" s="85"/>
-      <c r="F38" s="85"/>
-      <c r="G38" s="85"/>
+    <row r="38" spans="1:10" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="180" t="s">
+        <v>177</v>
+      </c>
+      <c r="B38" s="181"/>
+      <c r="C38" s="181"/>
+      <c r="D38" s="181"/>
+      <c r="E38" s="181"/>
+      <c r="F38" s="181"/>
+      <c r="G38" s="182"/>
       <c r="H38" s="82">
-        <v>18500</v>
-      </c>
-      <c r="J38" s="87"/>
+        <v>-58000</v>
+      </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="85" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="B39" s="161"/>
       <c r="C39" s="154"/>
@@ -4866,58 +4867,60 @@
       <c r="F39" s="154"/>
       <c r="G39" s="154"/>
       <c r="H39" s="82">
-        <v>58000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="85" t="s">
+        <v>53150</v>
+      </c>
+      <c r="I39" s="149"/>
+      <c r="J39" s="183"/>
+    </row>
+    <row r="40" spans="1:10" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="180" t="s">
+        <v>174</v>
+      </c>
+      <c r="B40" s="181"/>
+      <c r="C40" s="181"/>
+      <c r="D40" s="181"/>
+      <c r="E40" s="181"/>
+      <c r="F40" s="181"/>
+      <c r="G40" s="182"/>
+      <c r="H40" s="82">
+        <f>500000+245000</f>
+        <v>745000</v>
+      </c>
+      <c r="J40" s="183"/>
+    </row>
+    <row r="41" spans="1:10" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="96" t="s">
         <v>181</v>
       </c>
-      <c r="B40" s="161"/>
-      <c r="C40" s="154"/>
-      <c r="D40" s="154"/>
-      <c r="E40" s="154"/>
-      <c r="F40" s="154"/>
-      <c r="G40" s="154"/>
-      <c r="H40" s="238">
-        <v>53150</v>
-      </c>
-      <c r="I40" s="149"/>
-      <c r="J40" s="177"/>
-    </row>
-    <row r="41" spans="1:10" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="235" t="s">
-        <v>171</v>
-      </c>
-      <c r="B41" s="236"/>
-      <c r="C41" s="236"/>
-      <c r="D41" s="236"/>
-      <c r="E41" s="236"/>
-      <c r="F41" s="236"/>
-      <c r="G41" s="237"/>
+      <c r="B41" s="168"/>
+      <c r="C41" s="168"/>
+      <c r="D41" s="168"/>
+      <c r="E41" s="168"/>
+      <c r="F41" s="168"/>
+      <c r="G41" s="169"/>
       <c r="H41" s="82">
-        <v>450000</v>
-      </c>
-      <c r="J41" s="177"/>
+        <v>500000</v>
+      </c>
+      <c r="J41" s="183"/>
     </row>
     <row r="42" spans="1:10" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="190" t="s">
-        <v>180</v>
-      </c>
-      <c r="B42" s="191"/>
-      <c r="C42" s="191"/>
-      <c r="D42" s="191"/>
-      <c r="E42" s="191"/>
-      <c r="F42" s="191"/>
-      <c r="G42" s="192"/>
-      <c r="H42" s="238">
-        <v>741000</v>
-      </c>
-      <c r="J42" s="177"/>
+      <c r="A42" s="96" t="s">
+        <v>176</v>
+      </c>
+      <c r="B42" s="168"/>
+      <c r="C42" s="168"/>
+      <c r="D42" s="168"/>
+      <c r="E42" s="168"/>
+      <c r="F42" s="168"/>
+      <c r="G42" s="169"/>
+      <c r="H42" s="82">
+        <v>1200000</v>
+      </c>
+      <c r="J42" s="183"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="85" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="B43" s="161"/>
       <c r="C43" s="154"/>
@@ -4925,14 +4928,14 @@
       <c r="E43" s="154"/>
       <c r="F43" s="154"/>
       <c r="G43" s="154"/>
-      <c r="H43" s="238">
+      <c r="H43" s="82">
         <v>160000</v>
       </c>
-      <c r="J43" s="177"/>
+      <c r="J43" s="183"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="239" t="s">
-        <v>178</v>
+      <c r="A44" s="85" t="s">
+        <v>180</v>
       </c>
       <c r="B44" s="161"/>
       <c r="C44" s="154"/>
@@ -4940,177 +4943,178 @@
       <c r="E44" s="154"/>
       <c r="F44" s="154"/>
       <c r="G44" s="154"/>
-      <c r="H44" s="238">
-        <v>156892.12</v>
-      </c>
+      <c r="H44" s="82">
+        <v>57535</v>
+      </c>
+      <c r="J44" s="167"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="154" t="s">
-        <v>100</v>
-      </c>
-      <c r="B45" s="154"/>
+      <c r="A45" s="85" t="s">
+        <v>175</v>
+      </c>
+      <c r="B45" s="161"/>
       <c r="C45" s="154"/>
       <c r="D45" s="154"/>
       <c r="E45" s="154"/>
       <c r="F45" s="154"/>
       <c r="G45" s="154"/>
-      <c r="H45" s="84">
-        <f>SUM(H35:H44)</f>
-        <v>1817542.12</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="218" t="s">
+      <c r="H45" s="82">
+        <v>156892.12</v>
+      </c>
+      <c r="I45" s="149"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="154" t="s">
+        <v>100</v>
+      </c>
+      <c r="B46" s="154"/>
+      <c r="C46" s="154"/>
+      <c r="D46" s="154"/>
+      <c r="E46" s="154"/>
+      <c r="F46" s="154"/>
+      <c r="G46" s="154"/>
+      <c r="H46" s="84">
+        <f>SUM(H35:H45)</f>
+        <v>2994577.12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="221" t="s">
         <v>114</v>
       </c>
-      <c r="B46" s="218"/>
-      <c r="C46" s="218"/>
-      <c r="D46" s="218"/>
-      <c r="E46" s="218"/>
-      <c r="F46" s="218"/>
-      <c r="G46" s="218"/>
-      <c r="H46" s="218"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="154" t="s">
+      <c r="B47" s="221"/>
+      <c r="C47" s="221"/>
+      <c r="D47" s="221"/>
+      <c r="E47" s="221"/>
+      <c r="F47" s="221"/>
+      <c r="G47" s="221"/>
+      <c r="H47" s="221"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="154" t="s">
         <v>115</v>
       </c>
-      <c r="B47" s="154"/>
-      <c r="C47" s="154" t="s">
-        <v>177</v>
-      </c>
-      <c r="D47" s="163"/>
-      <c r="E47" s="154"/>
-      <c r="F47" s="154"/>
-      <c r="G47" s="154"/>
-      <c r="H47" s="82">
-        <v>250000</v>
-      </c>
-      <c r="J47" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="164" t="s">
-        <v>148</v>
-      </c>
       <c r="B48" s="154"/>
-      <c r="C48" s="198"/>
-      <c r="D48" s="199"/>
-      <c r="E48" s="165"/>
-      <c r="F48" s="158"/>
+      <c r="C48" s="154" t="s">
+        <v>169</v>
+      </c>
+      <c r="D48" s="163"/>
+      <c r="E48" s="154"/>
+      <c r="F48" s="154"/>
       <c r="G48" s="154"/>
       <c r="H48" s="82">
-        <v>28000</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" s="154"/>
+        <v>250000</v>
+      </c>
+      <c r="J48" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="164" t="s">
+        <v>147</v>
+      </c>
       <c r="B49" s="154"/>
-      <c r="C49" s="158"/>
-      <c r="D49" s="158"/>
-      <c r="E49" s="158"/>
+      <c r="C49" s="201"/>
+      <c r="D49" s="202"/>
+      <c r="E49" s="165"/>
       <c r="F49" s="158"/>
       <c r="G49" s="154"/>
-      <c r="H49" s="82"/>
+      <c r="H49" s="82">
+        <v>28000</v>
+      </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" s="157" t="s">
+      <c r="A50" s="154"/>
+      <c r="B50" s="154"/>
+      <c r="C50" s="158"/>
+      <c r="D50" s="158"/>
+      <c r="E50" s="158"/>
+      <c r="F50" s="158"/>
+      <c r="G50" s="154"/>
+      <c r="H50" s="82"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="157" t="s">
         <v>100</v>
       </c>
-      <c r="B50" s="157"/>
-      <c r="C50" s="157"/>
-      <c r="D50" s="157"/>
-      <c r="E50" s="157"/>
-      <c r="F50" s="157"/>
-      <c r="G50" s="157"/>
-      <c r="H50" s="84">
-        <f>SUM(H47:H49)</f>
+      <c r="B51" s="157"/>
+      <c r="C51" s="157"/>
+      <c r="D51" s="157"/>
+      <c r="E51" s="157"/>
+      <c r="F51" s="157"/>
+      <c r="G51" s="157"/>
+      <c r="H51" s="84">
+        <f>SUM(H48:H50)</f>
         <v>278000</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="229" t="s">
+    <row r="52" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="232" t="s">
         <v>116</v>
       </c>
-      <c r="B51" s="230"/>
-      <c r="C51" s="230"/>
-      <c r="D51" s="230"/>
-      <c r="E51" s="230"/>
-      <c r="F51" s="230"/>
-      <c r="G51" s="230"/>
-      <c r="H51" s="231"/>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" s="154" t="s">
+      <c r="B52" s="233"/>
+      <c r="C52" s="233"/>
+      <c r="D52" s="233"/>
+      <c r="E52" s="233"/>
+      <c r="F52" s="233"/>
+      <c r="G52" s="233"/>
+      <c r="H52" s="234"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="154" t="s">
         <v>117</v>
       </c>
-      <c r="B52" s="154"/>
-      <c r="C52" s="154"/>
-      <c r="D52" s="154"/>
-      <c r="E52" s="154"/>
-      <c r="F52" s="154"/>
-      <c r="G52" s="154"/>
-      <c r="H52" s="82">
-        <v>69571.37</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" s="154"/>
       <c r="B53" s="154"/>
       <c r="C53" s="154"/>
       <c r="D53" s="154"/>
       <c r="E53" s="154"/>
       <c r="F53" s="154"/>
       <c r="G53" s="154"/>
-      <c r="H53" s="82"/>
+      <c r="H53" s="82">
+        <v>89235.14</v>
+      </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" s="157" t="s">
+      <c r="A54" s="154"/>
+      <c r="B54" s="154"/>
+      <c r="C54" s="154"/>
+      <c r="D54" s="154"/>
+      <c r="E54" s="154"/>
+      <c r="F54" s="154"/>
+      <c r="G54" s="154"/>
+      <c r="H54" s="82"/>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="157" t="s">
         <v>106</v>
       </c>
-      <c r="B54" s="157"/>
-      <c r="C54" s="157"/>
-      <c r="D54" s="157"/>
-      <c r="E54" s="157"/>
-      <c r="F54" s="157"/>
-      <c r="G54" s="157"/>
-      <c r="H54" s="160">
-        <f>SUM(H52:H53)</f>
-        <v>69571.37</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="229" t="s">
+      <c r="B55" s="157"/>
+      <c r="C55" s="157"/>
+      <c r="D55" s="157"/>
+      <c r="E55" s="157"/>
+      <c r="F55" s="157"/>
+      <c r="G55" s="157"/>
+      <c r="H55" s="160">
+        <f>SUM(H53:H54)</f>
+        <v>89235.14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A56" s="232" t="s">
         <v>118</v>
       </c>
-      <c r="B55" s="230"/>
-      <c r="C55" s="230"/>
-      <c r="D55" s="230"/>
-      <c r="E55" s="230"/>
-      <c r="F55" s="230"/>
-      <c r="G55" s="230"/>
-      <c r="H55" s="231"/>
-      <c r="I55" s="87"/>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="85" t="s">
-        <v>140</v>
-      </c>
-      <c r="B56" s="85"/>
-      <c r="C56" s="85"/>
-      <c r="D56" s="85"/>
-      <c r="E56" s="85"/>
-      <c r="F56" s="85"/>
-      <c r="G56" s="85"/>
-      <c r="H56" s="82">
-        <v>49889.86</v>
-      </c>
+      <c r="B56" s="233"/>
+      <c r="C56" s="233"/>
+      <c r="D56" s="233"/>
+      <c r="E56" s="233"/>
+      <c r="F56" s="233"/>
+      <c r="G56" s="233"/>
+      <c r="H56" s="234"/>
       <c r="I56" s="87"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="85" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B57" s="85"/>
       <c r="C57" s="85"/>
@@ -5119,13 +5123,13 @@
       <c r="F57" s="85"/>
       <c r="G57" s="85"/>
       <c r="H57" s="82">
-        <v>3498.02</v>
+        <v>49889.86</v>
       </c>
       <c r="I57" s="87"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="85" t="s">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="B58" s="85"/>
       <c r="C58" s="85"/>
@@ -5133,34 +5137,39 @@
       <c r="E58" s="85"/>
       <c r="F58" s="85"/>
       <c r="G58" s="85"/>
-      <c r="H58" s="84">
-        <f>SUM(H56:H57)</f>
+      <c r="H58" s="82">
+        <v>3498.02</v>
+      </c>
+      <c r="I58" s="87"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" s="85" t="s">
+        <v>100</v>
+      </c>
+      <c r="B59" s="85"/>
+      <c r="C59" s="85"/>
+      <c r="D59" s="85"/>
+      <c r="E59" s="85"/>
+      <c r="F59" s="85"/>
+      <c r="G59" s="85"/>
+      <c r="H59" s="84">
+        <f>SUM(H57:H58)</f>
         <v>53387.88</v>
       </c>
-      <c r="I58" s="87"/>
-      <c r="K58" s="83"/>
-    </row>
-    <row r="59" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A59" s="232" t="s">
+      <c r="I59" s="87"/>
+      <c r="K59" s="83"/>
+    </row>
+    <row r="60" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A60" s="203" t="s">
         <v>119</v>
       </c>
-      <c r="B59" s="233"/>
-      <c r="C59" s="233"/>
-      <c r="D59" s="233"/>
-      <c r="E59" s="233"/>
-      <c r="F59" s="233"/>
-      <c r="G59" s="233"/>
-      <c r="H59" s="234"/>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" s="86"/>
-      <c r="B60" s="86"/>
-      <c r="C60" s="86"/>
-      <c r="D60" s="86"/>
-      <c r="E60" s="86"/>
-      <c r="F60" s="86"/>
-      <c r="G60" s="86"/>
-      <c r="H60" s="90"/>
+      <c r="B60" s="204"/>
+      <c r="C60" s="204"/>
+      <c r="D60" s="204"/>
+      <c r="E60" s="204"/>
+      <c r="F60" s="204"/>
+      <c r="G60" s="204"/>
+      <c r="H60" s="235"/>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="86"/>
@@ -5172,61 +5181,61 @@
       <c r="G61" s="86"/>
       <c r="H61" s="90"/>
     </row>
-    <row r="62" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="91" t="s">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" s="86"/>
+      <c r="B62" s="86"/>
+      <c r="C62" s="86"/>
+      <c r="D62" s="86"/>
+      <c r="E62" s="86"/>
+      <c r="F62" s="86"/>
+      <c r="G62" s="86"/>
+      <c r="H62" s="90"/>
+    </row>
+    <row r="63" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A63" s="91" t="s">
         <v>100</v>
       </c>
-      <c r="B62" s="89"/>
-      <c r="C62" s="89"/>
-      <c r="D62" s="89"/>
-      <c r="E62" s="89"/>
-      <c r="F62" s="89"/>
-      <c r="G62" s="89"/>
-      <c r="H62" s="92"/>
-    </row>
-    <row r="63" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="93"/>
-      <c r="B63" s="132"/>
-      <c r="C63" s="132"/>
-      <c r="D63" s="132"/>
-      <c r="E63" s="132"/>
-      <c r="F63" s="132"/>
-      <c r="G63" s="132"/>
-      <c r="H63" s="94"/>
-    </row>
-    <row r="64" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="91"/>
-      <c r="B64" s="89"/>
-      <c r="C64" s="89"/>
-      <c r="D64" s="89"/>
-      <c r="E64" s="89"/>
-      <c r="F64" s="89"/>
-      <c r="G64" s="89"/>
-      <c r="H64" s="92"/>
-    </row>
-    <row r="65" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="200" t="s">
-        <v>153</v>
-      </c>
-      <c r="B65" s="201"/>
-      <c r="C65" s="201"/>
-      <c r="D65" s="201"/>
-      <c r="E65" s="201"/>
-      <c r="F65" s="201"/>
-      <c r="G65" s="201"/>
-      <c r="H65" s="128"/>
-    </row>
-    <row r="66" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="91"/>
-      <c r="B66" s="89"/>
-      <c r="C66" s="89"/>
-      <c r="D66" s="89"/>
-      <c r="E66" s="89"/>
-      <c r="F66" s="89"/>
-      <c r="G66" s="89"/>
-      <c r="H66" s="92"/>
-    </row>
-    <row r="67" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="89"/>
+      <c r="C63" s="89"/>
+      <c r="D63" s="89"/>
+      <c r="E63" s="89"/>
+      <c r="F63" s="89"/>
+      <c r="G63" s="89"/>
+      <c r="H63" s="92"/>
+    </row>
+    <row r="64" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A64" s="93"/>
+      <c r="B64" s="132"/>
+      <c r="C64" s="132"/>
+      <c r="D64" s="132"/>
+      <c r="E64" s="132"/>
+      <c r="F64" s="132"/>
+      <c r="G64" s="132"/>
+      <c r="H64" s="94"/>
+    </row>
+    <row r="65" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="91"/>
+      <c r="B65" s="89"/>
+      <c r="C65" s="89"/>
+      <c r="D65" s="89"/>
+      <c r="E65" s="89"/>
+      <c r="F65" s="89"/>
+      <c r="G65" s="89"/>
+      <c r="H65" s="92"/>
+    </row>
+    <row r="66" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="203" t="s">
+        <v>152</v>
+      </c>
+      <c r="B66" s="204"/>
+      <c r="C66" s="204"/>
+      <c r="D66" s="204"/>
+      <c r="E66" s="204"/>
+      <c r="F66" s="204"/>
+      <c r="G66" s="204"/>
+      <c r="H66" s="128"/>
+    </row>
+    <row r="67" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="91"/>
       <c r="B67" s="89"/>
       <c r="C67" s="89"/>
@@ -5236,88 +5245,86 @@
       <c r="G67" s="89"/>
       <c r="H67" s="92"/>
     </row>
-    <row r="68" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="129" t="s">
+    <row r="68" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="91"/>
+      <c r="B68" s="89"/>
+      <c r="C68" s="89"/>
+      <c r="D68" s="89"/>
+      <c r="E68" s="89"/>
+      <c r="F68" s="89"/>
+      <c r="G68" s="89"/>
+      <c r="H68" s="92"/>
+    </row>
+    <row r="69" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="129" t="s">
         <v>100</v>
       </c>
-      <c r="B68" s="132"/>
-      <c r="C68" s="132"/>
-      <c r="D68" s="132"/>
-      <c r="E68" s="132"/>
-      <c r="F68" s="132"/>
-      <c r="G68" s="132"/>
-      <c r="H68" s="94">
-        <f>SUM(H66:H67)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A69" s="91"/>
-      <c r="B69" s="89"/>
-      <c r="C69" s="89"/>
-      <c r="D69" s="89"/>
-      <c r="E69" s="89"/>
-      <c r="F69" s="89"/>
-      <c r="G69" s="89"/>
-      <c r="H69" s="92"/>
-    </row>
-    <row r="70" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A70" s="189" t="s">
+      <c r="B69" s="132"/>
+      <c r="C69" s="132"/>
+      <c r="D69" s="132"/>
+      <c r="E69" s="132"/>
+      <c r="F69" s="132"/>
+      <c r="G69" s="132"/>
+      <c r="H69" s="94">
+        <f>SUM(H67:H68)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A70" s="91"/>
+      <c r="B70" s="89"/>
+      <c r="C70" s="89"/>
+      <c r="D70" s="89"/>
+      <c r="E70" s="89"/>
+      <c r="F70" s="89"/>
+      <c r="G70" s="89"/>
+      <c r="H70" s="92"/>
+    </row>
+    <row r="71" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A71" s="195" t="s">
         <v>120</v>
       </c>
-      <c r="B70" s="189"/>
-      <c r="C70" s="189"/>
-      <c r="D70" s="189"/>
-      <c r="E70" s="189"/>
-      <c r="F70" s="189"/>
-      <c r="G70" s="189"/>
-      <c r="H70" s="95"/>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A71" s="190"/>
-      <c r="B71" s="191"/>
-      <c r="C71" s="191"/>
-      <c r="D71" s="191"/>
-      <c r="E71" s="191"/>
-      <c r="F71" s="191"/>
-      <c r="G71" s="192"/>
-      <c r="H71" s="124"/>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A72" s="96"/>
-      <c r="B72" s="97"/>
-      <c r="C72" s="97"/>
-      <c r="D72" s="97"/>
-      <c r="E72" s="97"/>
-      <c r="F72" s="97"/>
-      <c r="G72" s="98"/>
+      <c r="B71" s="195"/>
+      <c r="C71" s="195"/>
+      <c r="D71" s="195"/>
+      <c r="E71" s="195"/>
+      <c r="F71" s="195"/>
+      <c r="G71" s="195"/>
+      <c r="H71" s="95"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="180"/>
+      <c r="B72" s="181"/>
+      <c r="C72" s="181"/>
+      <c r="D72" s="181"/>
+      <c r="E72" s="181"/>
+      <c r="F72" s="181"/>
+      <c r="G72" s="182"/>
       <c r="H72" s="124"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A73" s="193"/>
-      <c r="B73" s="194"/>
-      <c r="C73" s="194"/>
-      <c r="D73" s="194"/>
-      <c r="E73" s="194"/>
-      <c r="F73" s="194"/>
-      <c r="G73" s="195"/>
-      <c r="H73" s="82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" s="133"/>
-      <c r="B74" s="134"/>
-      <c r="C74" s="134"/>
-      <c r="D74" s="134"/>
-      <c r="E74" s="134"/>
-      <c r="F74" s="134"/>
-      <c r="G74" s="135"/>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="96"/>
+      <c r="B73" s="97"/>
+      <c r="C73" s="97"/>
+      <c r="D73" s="97"/>
+      <c r="E73" s="97"/>
+      <c r="F73" s="97"/>
+      <c r="G73" s="98"/>
+      <c r="H73" s="124"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="196"/>
+      <c r="B74" s="197"/>
+      <c r="C74" s="197"/>
+      <c r="D74" s="197"/>
+      <c r="E74" s="197"/>
+      <c r="F74" s="197"/>
+      <c r="G74" s="198"/>
       <c r="H74" s="82">
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="133"/>
       <c r="B75" s="134"/>
       <c r="C75" s="134"/>
@@ -5329,177 +5336,179 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A76" s="137" t="s">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="133"/>
+      <c r="B76" s="134"/>
+      <c r="C76" s="134"/>
+      <c r="D76" s="134"/>
+      <c r="E76" s="134"/>
+      <c r="F76" s="134"/>
+      <c r="G76" s="135"/>
+      <c r="H76" s="82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="137" t="s">
         <v>100</v>
       </c>
-      <c r="B76" s="85"/>
-      <c r="C76" s="85"/>
-      <c r="D76" s="85"/>
-      <c r="E76" s="85"/>
-      <c r="F76" s="85"/>
-      <c r="G76" s="85"/>
-      <c r="H76" s="84">
-        <f>SUM(H71:H75)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="138"/>
-      <c r="B77" s="138"/>
-      <c r="C77" s="138"/>
-      <c r="D77" s="138"/>
-      <c r="E77" s="138"/>
-      <c r="F77" s="138"/>
-      <c r="G77" s="138"/>
-      <c r="H77" s="139"/>
-      <c r="I77" s="87"/>
-    </row>
-    <row r="78" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="196" t="s">
+      <c r="B77" s="85"/>
+      <c r="C77" s="85"/>
+      <c r="D77" s="85"/>
+      <c r="E77" s="85"/>
+      <c r="F77" s="85"/>
+      <c r="G77" s="85"/>
+      <c r="H77" s="84">
+        <f>SUM(H72:H76)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="138"/>
+      <c r="B78" s="138"/>
+      <c r="C78" s="138"/>
+      <c r="D78" s="138"/>
+      <c r="E78" s="138"/>
+      <c r="F78" s="138"/>
+      <c r="G78" s="138"/>
+      <c r="H78" s="139"/>
+      <c r="I78" s="87"/>
+    </row>
+    <row r="79" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="199" t="s">
         <v>121</v>
       </c>
-      <c r="B78" s="197"/>
-      <c r="C78" s="197"/>
-      <c r="D78" s="197"/>
-      <c r="E78" s="197"/>
-      <c r="F78" s="197"/>
-      <c r="G78" s="197"/>
-      <c r="H78" s="140">
-        <f>H76</f>
-        <v>0</v>
-      </c>
-      <c r="I78" s="87"/>
-    </row>
-    <row r="79" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="186" t="s">
+      <c r="B79" s="200"/>
+      <c r="C79" s="200"/>
+      <c r="D79" s="200"/>
+      <c r="E79" s="200"/>
+      <c r="F79" s="200"/>
+      <c r="G79" s="200"/>
+      <c r="H79" s="140">
+        <f>H77</f>
+        <v>0</v>
+      </c>
+      <c r="I79" s="87"/>
+    </row>
+    <row r="80" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="192" t="s">
         <v>122</v>
       </c>
-      <c r="B79" s="187"/>
-      <c r="C79" s="187"/>
-      <c r="D79" s="187"/>
-      <c r="E79" s="187"/>
-      <c r="F79" s="187"/>
-      <c r="G79" s="188"/>
-      <c r="H79" s="140"/>
-      <c r="I79" s="88"/>
-    </row>
-    <row r="80" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="202" t="s">
+      <c r="B80" s="193"/>
+      <c r="C80" s="193"/>
+      <c r="D80" s="193"/>
+      <c r="E80" s="193"/>
+      <c r="F80" s="193"/>
+      <c r="G80" s="194"/>
+      <c r="H80" s="140"/>
+      <c r="I80" s="88"/>
+    </row>
+    <row r="81" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="205" t="s">
         <v>142</v>
       </c>
-      <c r="B80" s="203"/>
-      <c r="C80" s="203"/>
-      <c r="D80" s="203"/>
-      <c r="E80" s="203"/>
-      <c r="F80" s="203"/>
-      <c r="G80" s="204"/>
-      <c r="H80" s="140"/>
-      <c r="I80" s="87"/>
-      <c r="J80" s="83"/>
-    </row>
-    <row r="81" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A81" s="196" t="s">
+      <c r="B81" s="206"/>
+      <c r="C81" s="206"/>
+      <c r="D81" s="206"/>
+      <c r="E81" s="206"/>
+      <c r="F81" s="206"/>
+      <c r="G81" s="207"/>
+      <c r="H81" s="140"/>
+      <c r="I81" s="87"/>
+      <c r="J81" s="83"/>
+    </row>
+    <row r="82" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A82" s="199" t="s">
         <v>123</v>
       </c>
-      <c r="B81" s="197"/>
-      <c r="C81" s="197"/>
-      <c r="D81" s="197"/>
-      <c r="E81" s="197"/>
-      <c r="F81" s="197"/>
-      <c r="G81" s="197"/>
-      <c r="H81" s="140">
-        <f>H62+H58+H54+H50+H45+H33+H16+H21+H28+H68</f>
-        <v>5181332.3999999994</v>
-      </c>
-      <c r="I81" s="83"/>
-    </row>
-    <row r="82" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A82" s="205" t="s">
+      <c r="B82" s="200"/>
+      <c r="C82" s="200"/>
+      <c r="D82" s="200"/>
+      <c r="E82" s="200"/>
+      <c r="F82" s="200"/>
+      <c r="G82" s="200"/>
+      <c r="H82" s="140">
+        <f>H63+H59+H55+H51+H46+H33+H16+H21+H28+H69</f>
+        <v>6696913.4500000002</v>
+      </c>
+      <c r="I82" s="83"/>
+    </row>
+    <row r="83" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A83" s="208" t="s">
         <v>124</v>
       </c>
-      <c r="B82" s="206"/>
-      <c r="C82" s="206"/>
-      <c r="D82" s="206"/>
-      <c r="E82" s="206"/>
-      <c r="F82" s="206"/>
-      <c r="G82" s="207"/>
-      <c r="H82" s="141">
-        <f>H81+H79</f>
-        <v>5181332.3999999994</v>
-      </c>
-      <c r="I82" s="83"/>
-      <c r="K82" s="149"/>
-    </row>
-    <row r="83" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A83" s="205" t="s">
+      <c r="B83" s="209"/>
+      <c r="C83" s="209"/>
+      <c r="D83" s="209"/>
+      <c r="E83" s="209"/>
+      <c r="F83" s="209"/>
+      <c r="G83" s="210"/>
+      <c r="H83" s="141">
+        <f>H82+H80</f>
+        <v>6696913.4500000002</v>
+      </c>
+      <c r="I83" s="83"/>
+      <c r="K83" s="149"/>
+    </row>
+    <row r="84" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A84" s="208" t="s">
         <v>125</v>
-      </c>
-      <c r="B83" s="206"/>
-      <c r="C83" s="206"/>
-      <c r="D83" s="206"/>
-      <c r="E83" s="206"/>
-      <c r="F83" s="206"/>
-      <c r="G83" s="207"/>
-      <c r="H83" s="142">
-        <f>H78+H80</f>
-        <v>0</v>
-      </c>
-      <c r="I83" s="83"/>
-    </row>
-    <row r="84" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="208" t="s">
-        <v>126</v>
       </c>
       <c r="B84" s="209"/>
       <c r="C84" s="209"/>
       <c r="D84" s="209"/>
       <c r="E84" s="209"/>
       <c r="F84" s="209"/>
-      <c r="G84" s="209"/>
-      <c r="H84" s="143">
-        <f>H81+H78</f>
-        <v>5181332.3999999994</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="210" t="s">
+      <c r="G84" s="210"/>
+      <c r="H84" s="142">
+        <f>H79+H81</f>
+        <v>0</v>
+      </c>
+      <c r="I84" s="83"/>
+    </row>
+    <row r="85" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="211" t="s">
+        <v>126</v>
+      </c>
+      <c r="B85" s="212"/>
+      <c r="C85" s="212"/>
+      <c r="D85" s="212"/>
+      <c r="E85" s="212"/>
+      <c r="F85" s="212"/>
+      <c r="G85" s="212"/>
+      <c r="H85" s="143">
+        <f>H82+H79</f>
+        <v>6696913.4500000002</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="213" t="s">
         <v>127</v>
       </c>
-      <c r="B85" s="211"/>
-      <c r="C85" s="211"/>
-      <c r="D85" s="211"/>
-      <c r="E85" s="211"/>
-      <c r="F85" s="211"/>
-      <c r="G85" s="211"/>
-      <c r="H85" s="100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="101"/>
-      <c r="B86" s="101"/>
-      <c r="C86" s="101"/>
-      <c r="D86" s="101"/>
-      <c r="E86" s="101"/>
-      <c r="F86" s="101"/>
-      <c r="G86" s="101"/>
-      <c r="H86" s="102"/>
-    </row>
-    <row r="87" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="212" t="s">
-        <v>162</v>
-      </c>
-      <c r="B87" s="213"/>
-      <c r="C87" s="213"/>
-      <c r="D87" s="213"/>
-      <c r="E87" s="213"/>
-      <c r="F87" s="213"/>
-      <c r="G87" s="213"/>
-      <c r="H87" s="214"/>
-    </row>
-    <row r="88" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="215"/>
+      <c r="B86" s="214"/>
+      <c r="C86" s="214"/>
+      <c r="D86" s="214"/>
+      <c r="E86" s="214"/>
+      <c r="F86" s="214"/>
+      <c r="G86" s="214"/>
+      <c r="H86" s="100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="101"/>
+      <c r="B87" s="101"/>
+      <c r="C87" s="101"/>
+      <c r="D87" s="101"/>
+      <c r="E87" s="101"/>
+      <c r="F87" s="101"/>
+      <c r="G87" s="101"/>
+      <c r="H87" s="102"/>
+    </row>
+    <row r="88" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="215" t="s">
+        <v>161</v>
+      </c>
       <c r="B88" s="216"/>
       <c r="C88" s="216"/>
       <c r="D88" s="216"/>
@@ -5508,75 +5517,70 @@
       <c r="G88" s="216"/>
       <c r="H88" s="217"/>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A89" s="6"/>
-      <c r="B89" s="6"/>
-      <c r="C89" s="6"/>
-      <c r="D89" s="6"/>
-      <c r="E89" s="6"/>
-      <c r="F89" s="6"/>
-      <c r="G89" s="6"/>
-      <c r="H89" s="6"/>
-    </row>
-    <row r="90" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A90" s="178" t="s">
+    <row r="89" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="218"/>
+      <c r="B89" s="219"/>
+      <c r="C89" s="219"/>
+      <c r="D89" s="219"/>
+      <c r="E89" s="219"/>
+      <c r="F89" s="219"/>
+      <c r="G89" s="219"/>
+      <c r="H89" s="220"/>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" s="6"/>
+      <c r="B90" s="6"/>
+      <c r="C90" s="6"/>
+      <c r="D90" s="6"/>
+      <c r="E90" s="6"/>
+      <c r="F90" s="6"/>
+      <c r="G90" s="6"/>
+      <c r="H90" s="6"/>
+    </row>
+    <row r="91" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A91" s="184" t="s">
         <v>128</v>
       </c>
-      <c r="B90" s="179"/>
-      <c r="C90" s="179"/>
-      <c r="D90" s="179"/>
-      <c r="E90" s="179"/>
-      <c r="F90" s="179"/>
-      <c r="G90" s="179"/>
-      <c r="H90" s="180"/>
-    </row>
-    <row r="91" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A91" s="103" t="s">
+      <c r="B91" s="185"/>
+      <c r="C91" s="185"/>
+      <c r="D91" s="185"/>
+      <c r="E91" s="185"/>
+      <c r="F91" s="185"/>
+      <c r="G91" s="185"/>
+      <c r="H91" s="186"/>
+    </row>
+    <row r="92" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A92" s="103" t="s">
         <v>129</v>
       </c>
-      <c r="B91" s="104"/>
-      <c r="C91" s="104"/>
-      <c r="D91" s="104"/>
-      <c r="E91" s="104"/>
-      <c r="F91" s="104"/>
-      <c r="G91" s="104"/>
-      <c r="H91" s="105">
-        <v>1062593.9356154203</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A92" s="8" t="s">
+      <c r="B92" s="104"/>
+      <c r="C92" s="104"/>
+      <c r="D92" s="104"/>
+      <c r="E92" s="104"/>
+      <c r="F92" s="104"/>
+      <c r="G92" s="104"/>
+      <c r="H92" s="105">
+        <v>1280791.0346397704</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B92" s="106"/>
-      <c r="C92" s="106"/>
-      <c r="D92" s="106"/>
-      <c r="E92" s="106"/>
-      <c r="F92" s="106"/>
-      <c r="G92" s="106"/>
-      <c r="H92" s="18">
+      <c r="B93" s="106"/>
+      <c r="C93" s="106"/>
+      <c r="D93" s="106"/>
+      <c r="E93" s="106"/>
+      <c r="F93" s="106"/>
+      <c r="G93" s="106"/>
+      <c r="H93" s="18">
         <f>Planilla!G43</f>
-        <v>5845602.4266750002</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A93" s="107" t="s">
-        <v>136</v>
-      </c>
-      <c r="B93" s="108"/>
-      <c r="C93" s="108"/>
-      <c r="D93" s="108"/>
-      <c r="E93" s="108"/>
-      <c r="F93" s="108"/>
-      <c r="G93" s="108"/>
-      <c r="H93" s="123">
-        <f>-H84</f>
-        <v>-5181332.3999999994</v>
+        <v>4581518.1130966982</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="107" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B94" s="108"/>
       <c r="C94" s="108"/>
@@ -5584,14 +5588,14 @@
       <c r="E94" s="108"/>
       <c r="F94" s="108"/>
       <c r="G94" s="108"/>
-      <c r="H94" s="31">
-        <f>D110</f>
-        <v>0</v>
+      <c r="H94" s="123">
+        <f>-H85</f>
+        <v>-6696913.4500000002</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="107" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="B95" s="108"/>
       <c r="C95" s="108"/>
@@ -5599,85 +5603,82 @@
       <c r="E95" s="108"/>
       <c r="F95" s="108"/>
       <c r="G95" s="108"/>
-      <c r="H95" s="123">
-        <v>-155000</v>
+      <c r="H95" s="31">
+        <f>D109</f>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="107" t="s">
-        <v>172</v>
-      </c>
-      <c r="B96" s="108"/>
+        <v>153</v>
+      </c>
+      <c r="B96" s="109"/>
       <c r="C96" s="108"/>
       <c r="D96" s="108"/>
       <c r="E96" s="108"/>
       <c r="F96" s="108"/>
       <c r="G96" s="108"/>
-      <c r="H96" s="123">
-        <v>-5745.4976506499997</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="107" t="s">
-        <v>154</v>
-      </c>
-      <c r="B97" s="109"/>
-      <c r="C97" s="108"/>
-      <c r="D97" s="108"/>
-      <c r="E97" s="108"/>
-      <c r="F97" s="108"/>
-      <c r="G97" s="108"/>
-      <c r="H97" s="131">
-        <f>-H68</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A98" s="110" t="s">
+      <c r="H96" s="131">
+        <f>-H69</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A97" s="110" t="s">
         <v>132</v>
       </c>
-      <c r="B98" s="111"/>
-      <c r="C98" s="111"/>
-      <c r="D98" s="111"/>
-      <c r="E98" s="111"/>
-      <c r="F98" s="111"/>
-      <c r="G98" s="111"/>
-      <c r="H98" s="112">
-        <f>SUM(H91:H97)</f>
-        <v>1566118.464639771</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="100" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="181" t="s">
+      <c r="B97" s="111"/>
+      <c r="C97" s="111"/>
+      <c r="D97" s="111"/>
+      <c r="E97" s="111"/>
+      <c r="F97" s="111"/>
+      <c r="G97" s="111"/>
+      <c r="H97" s="112">
+        <f>SUM(H92:H96)</f>
+        <v>-834604.30226353183</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="99" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="187" t="s">
         <v>133</v>
       </c>
-      <c r="B100" s="182"/>
-      <c r="C100" s="182"/>
-      <c r="D100" s="182"/>
-      <c r="E100" s="182"/>
-      <c r="F100" s="182"/>
-      <c r="G100" s="182"/>
-      <c r="H100" s="183"/>
-    </row>
-    <row r="101" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A101" s="113" t="s">
+      <c r="B99" s="188"/>
+      <c r="C99" s="188"/>
+      <c r="D99" s="188"/>
+      <c r="E99" s="188"/>
+      <c r="F99" s="188"/>
+      <c r="G99" s="188"/>
+      <c r="H99" s="189"/>
+    </row>
+    <row r="100" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A100" s="113" t="s">
         <v>129</v>
       </c>
-      <c r="B101" s="113"/>
-      <c r="C101" s="113"/>
-      <c r="D101" s="113"/>
-      <c r="E101" s="113"/>
-      <c r="F101" s="113"/>
-      <c r="G101" s="113"/>
-      <c r="H101" s="114">
-        <v>0</v>
-      </c>
+      <c r="B100" s="113"/>
+      <c r="C100" s="113"/>
+      <c r="D100" s="113"/>
+      <c r="E100" s="113"/>
+      <c r="F100" s="113"/>
+      <c r="G100" s="113"/>
+      <c r="H100" s="114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="6"/>
+      <c r="B101" s="115"/>
+      <c r="C101" s="108"/>
+      <c r="D101" s="6"/>
+      <c r="E101" s="6"/>
+      <c r="F101" s="6"/>
+      <c r="G101" s="6"/>
+      <c r="H101" s="18"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="6"/>
-      <c r="B102" s="115"/>
-      <c r="C102" s="108"/>
+      <c r="B102" s="116"/>
+      <c r="C102" s="6"/>
       <c r="D102" s="6"/>
       <c r="E102" s="6"/>
       <c r="F102" s="6"/>
@@ -5686,7 +5687,7 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="6"/>
-      <c r="B103" s="116"/>
+      <c r="B103" s="6"/>
       <c r="C103" s="6"/>
       <c r="D103" s="6"/>
       <c r="E103" s="6"/>
@@ -5695,36 +5696,32 @@
       <c r="H103" s="18"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="6"/>
-      <c r="B104" s="6"/>
-      <c r="C104" s="6"/>
-      <c r="D104" s="6"/>
-      <c r="E104" s="6"/>
-      <c r="F104" s="6"/>
-      <c r="G104" s="6"/>
-      <c r="H104" s="18"/>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="117" t="s">
+      <c r="A104" s="117" t="s">
         <v>132</v>
       </c>
-      <c r="B105" s="117"/>
-      <c r="C105" s="117"/>
-      <c r="D105" s="117"/>
-      <c r="E105" s="117"/>
-      <c r="F105" s="117"/>
-      <c r="G105" s="117"/>
-      <c r="H105" s="118">
-        <v>0</v>
-      </c>
+      <c r="B104" s="117"/>
+      <c r="C104" s="117"/>
+      <c r="D104" s="117"/>
+      <c r="E104" s="117"/>
+      <c r="F104" s="117"/>
+      <c r="G104" s="117"/>
+      <c r="H104" s="118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="125" t="s">
+        <v>145</v>
+      </c>
+      <c r="B106" s="126"/>
+      <c r="C106" s="126"/>
+      <c r="D106" s="126"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="125" t="s">
-        <v>146</v>
-      </c>
-      <c r="B107" s="126"/>
-      <c r="C107" s="126"/>
-      <c r="D107" s="126"/>
+      <c r="A107" s="6"/>
+      <c r="B107" s="6"/>
+      <c r="C107" s="6"/>
+      <c r="D107" s="18"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="6"/>
@@ -5733,35 +5730,35 @@
       <c r="D108" s="18"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="6"/>
-      <c r="B109" s="6"/>
-      <c r="C109" s="6"/>
-      <c r="D109" s="18"/>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="119" t="s">
+      <c r="A109" s="119" t="s">
         <v>100</v>
       </c>
-      <c r="B110" s="126"/>
-      <c r="C110" s="126"/>
-      <c r="D110" s="136">
-        <f>SUM(D108:D109)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="125" t="s">
-        <v>147</v>
-      </c>
-      <c r="B112" s="119"/>
-      <c r="C112" s="119"/>
-      <c r="D112" s="119"/>
+      <c r="B109" s="126"/>
+      <c r="C109" s="126"/>
+      <c r="D109" s="136">
+        <f>SUM(D107:D108)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="125" t="s">
+        <v>146</v>
+      </c>
+      <c r="B111" s="119"/>
+      <c r="C111" s="119"/>
+      <c r="D111" s="119"/>
+    </row>
+    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="6"/>
+      <c r="B112" s="99"/>
+      <c r="C112" s="99"/>
+      <c r="D112" s="121"/>
     </row>
     <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="6"/>
-      <c r="B113" s="99"/>
-      <c r="C113" s="99"/>
-      <c r="D113" s="121"/>
+      <c r="B113" s="6"/>
+      <c r="C113" s="6"/>
+      <c r="D113" s="127"/>
     </row>
     <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="6"/>
@@ -5769,33 +5766,28 @@
       <c r="C114" s="6"/>
       <c r="D114" s="127"/>
     </row>
-    <row r="115" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="6"/>
       <c r="B115" s="6"/>
       <c r="C115" s="6"/>
       <c r="D115" s="127"/>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A116" s="6"/>
-      <c r="B116" s="6"/>
-      <c r="C116" s="6"/>
-      <c r="D116" s="127"/>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A117" s="120" t="s">
+      <c r="A116" s="120" t="s">
         <v>100</v>
       </c>
-      <c r="B117" s="120"/>
-      <c r="C117" s="184">
-        <f>SUM(D113:D116)</f>
-        <v>0</v>
-      </c>
-      <c r="D117" s="185"/>
+      <c r="B116" s="120"/>
+      <c r="C116" s="190">
+        <f>SUM(D112:D115)</f>
+        <v>0</v>
+      </c>
+      <c r="D116" s="191"/>
     </row>
   </sheetData>
   <mergeCells count="32">
     <mergeCell ref="A85:G85"/>
-    <mergeCell ref="A87:H88"/>
+    <mergeCell ref="A86:G86"/>
+    <mergeCell ref="A88:H89"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="E3:H3"/>
@@ -5804,24 +5796,23 @@
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="A34:H34"/>
-    <mergeCell ref="A46:H46"/>
-    <mergeCell ref="A51:H51"/>
-    <mergeCell ref="A55:H55"/>
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A42:G42"/>
-    <mergeCell ref="J40:J43"/>
-    <mergeCell ref="A90:H90"/>
-    <mergeCell ref="A100:H100"/>
-    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="J39:J43"/>
+    <mergeCell ref="A91:H91"/>
+    <mergeCell ref="A99:H99"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="A80:G80"/>
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A72:G72"/>
+    <mergeCell ref="A74:G74"/>
     <mergeCell ref="A79:G79"/>
-    <mergeCell ref="A70:G70"/>
-    <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A78:G78"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="A65:G65"/>
-    <mergeCell ref="A80:G80"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="A66:G66"/>
     <mergeCell ref="A81:G81"/>
     <mergeCell ref="A82:G82"/>
     <mergeCell ref="A83:G83"/>

--- a/YRIGOYEN 9115/Junio/YRIGOYEN-EXPENSAS-JUNIO.xlsx
+++ b/YRIGOYEN 9115/Junio/YRIGOYEN-EXPENSAS-JUNIO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\YRIGOYEN 9115\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D039CD5-7FD4-4E8D-843F-DF1C916ED276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA1F44B3-8AA8-4CAE-BD70-F391154860F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1690,6 +1690,8 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="16" fillId="10" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1720,6 +1722,87 @@
     <xf numFmtId="166" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="29" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1789,12 +1872,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1813,83 +1890,6 @@
     <xf numFmtId="0" fontId="30" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="29" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="10" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2374,13 +2374,13 @@
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
-      <c r="F3" s="170" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3" s="171"/>
-      <c r="H3" s="171"/>
-      <c r="I3" s="171"/>
-      <c r="J3" s="172"/>
+      <c r="F3" s="172" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3" s="173"/>
+      <c r="H3" s="173"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="174"/>
       <c r="K3" s="147"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
@@ -2395,11 +2395,11 @@
       <c r="C4" s="6"/>
       <c r="D4" s="8"/>
       <c r="E4" s="145"/>
-      <c r="F4" s="173"/>
-      <c r="G4" s="174"/>
-      <c r="H4" s="174"/>
-      <c r="I4" s="174"/>
-      <c r="J4" s="175"/>
+      <c r="F4" s="175"/>
+      <c r="G4" s="176"/>
+      <c r="H4" s="176"/>
+      <c r="I4" s="176"/>
+      <c r="J4" s="177"/>
       <c r="K4" s="147"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
@@ -2408,20 +2408,20 @@
     </row>
     <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15"/>
-      <c r="B5" s="179">
+      <c r="B5" s="181">
         <f>C3</f>
         <v>5000000</v>
       </c>
-      <c r="C5" s="179"/>
+      <c r="C5" s="181"/>
       <c r="D5" s="16"/>
       <c r="E5" s="146">
         <v>0</v>
       </c>
-      <c r="F5" s="173"/>
-      <c r="G5" s="174"/>
-      <c r="H5" s="174"/>
-      <c r="I5" s="174"/>
-      <c r="J5" s="175"/>
+      <c r="F5" s="175"/>
+      <c r="G5" s="176"/>
+      <c r="H5" s="176"/>
+      <c r="I5" s="176"/>
+      <c r="J5" s="177"/>
       <c r="K5" s="148"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
@@ -2436,11 +2436,11 @@
       <c r="C6" s="18"/>
       <c r="D6" s="16"/>
       <c r="E6" s="145"/>
-      <c r="F6" s="176"/>
-      <c r="G6" s="177"/>
-      <c r="H6" s="177"/>
-      <c r="I6" s="177"/>
-      <c r="J6" s="178"/>
+      <c r="F6" s="178"/>
+      <c r="G6" s="179"/>
+      <c r="H6" s="179"/>
+      <c r="I6" s="179"/>
+      <c r="J6" s="180"/>
       <c r="K6" s="148"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
@@ -2449,11 +2449,11 @@
     </row>
     <row r="7" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15"/>
-      <c r="B7" s="179">
+      <c r="B7" s="181">
         <f>C2</f>
         <v>0</v>
       </c>
-      <c r="C7" s="179"/>
+      <c r="C7" s="181"/>
       <c r="D7" s="16"/>
       <c r="E7" s="18"/>
       <c r="F7" s="32"/>
@@ -4035,7 +4035,7 @@
       <c r="F38" s="18">
         <v>344673.7297766995</v>
       </c>
-      <c r="G38" s="236">
+      <c r="G38" s="170">
         <v>107500</v>
       </c>
       <c r="H38" s="32">
@@ -4331,7 +4331,7 @@
       <c r="P43" s="69"/>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G45" s="237" t="s">
+      <c r="G45" s="171" t="s">
         <v>182</v>
       </c>
     </row>
@@ -4375,23 +4375,23 @@
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="38"/>
-      <c r="D2" s="222"/>
-      <c r="E2" s="223"/>
-      <c r="F2" s="223"/>
-      <c r="G2" s="223"/>
-      <c r="H2" s="224"/>
+      <c r="D2" s="193"/>
+      <c r="E2" s="194"/>
+      <c r="F2" s="194"/>
+      <c r="G2" s="194"/>
+      <c r="H2" s="195"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="38"/>
       <c r="D3" s="74" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="225" t="s">
+      <c r="E3" s="196" t="s">
         <v>89</v>
       </c>
-      <c r="F3" s="225"/>
-      <c r="G3" s="225"/>
-      <c r="H3" s="226"/>
+      <c r="F3" s="196"/>
+      <c r="G3" s="196"/>
+      <c r="H3" s="197"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="38"/>
@@ -4459,16 +4459,16 @@
       <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="227" t="s">
+      <c r="A10" s="198" t="s">
         <v>98</v>
       </c>
-      <c r="B10" s="228"/>
-      <c r="C10" s="228"/>
-      <c r="D10" s="228"/>
-      <c r="E10" s="228"/>
-      <c r="F10" s="228"/>
-      <c r="G10" s="228"/>
-      <c r="H10" s="229"/>
+      <c r="B10" s="199"/>
+      <c r="C10" s="199"/>
+      <c r="D10" s="199"/>
+      <c r="E10" s="199"/>
+      <c r="F10" s="199"/>
+      <c r="G10" s="199"/>
+      <c r="H10" s="200"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="14"/>
@@ -4481,16 +4481,16 @@
       <c r="H11" s="6"/>
     </row>
     <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="230" t="s">
+      <c r="A12" s="201" t="s">
         <v>99</v>
       </c>
-      <c r="B12" s="230"/>
-      <c r="C12" s="230"/>
-      <c r="D12" s="230"/>
-      <c r="E12" s="230"/>
-      <c r="F12" s="230"/>
-      <c r="G12" s="230"/>
-      <c r="H12" s="230"/>
+      <c r="B12" s="201"/>
+      <c r="C12" s="201"/>
+      <c r="D12" s="201"/>
+      <c r="E12" s="201"/>
+      <c r="F12" s="201"/>
+      <c r="G12" s="201"/>
+      <c r="H12" s="201"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="153" t="s">
@@ -4552,16 +4552,16 @@
       <c r="I16" s="83"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="231" t="s">
+      <c r="A17" s="202" t="s">
         <v>164</v>
       </c>
-      <c r="B17" s="231"/>
-      <c r="C17" s="231"/>
-      <c r="D17" s="231"/>
-      <c r="E17" s="231"/>
-      <c r="F17" s="231"/>
-      <c r="G17" s="231"/>
-      <c r="H17" s="231"/>
+      <c r="B17" s="202"/>
+      <c r="C17" s="202"/>
+      <c r="D17" s="202"/>
+      <c r="E17" s="202"/>
+      <c r="F17" s="202"/>
+      <c r="G17" s="202"/>
+      <c r="H17" s="202"/>
     </row>
     <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="85" t="s">
@@ -4613,16 +4613,16 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="231" t="s">
+      <c r="A22" s="202" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="231"/>
-      <c r="C22" s="231"/>
-      <c r="D22" s="231"/>
-      <c r="E22" s="231"/>
-      <c r="F22" s="231"/>
-      <c r="G22" s="231"/>
-      <c r="H22" s="231"/>
+      <c r="B22" s="202"/>
+      <c r="C22" s="202"/>
+      <c r="D22" s="202"/>
+      <c r="E22" s="202"/>
+      <c r="F22" s="202"/>
+      <c r="G22" s="202"/>
+      <c r="H22" s="202"/>
     </row>
     <row r="23" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="153" t="s">
@@ -4718,16 +4718,16 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="221" t="s">
+      <c r="A29" s="192" t="s">
         <v>107</v>
       </c>
-      <c r="B29" s="221"/>
-      <c r="C29" s="221"/>
-      <c r="D29" s="221"/>
-      <c r="E29" s="221"/>
-      <c r="F29" s="221"/>
-      <c r="G29" s="221"/>
-      <c r="H29" s="221"/>
+      <c r="B29" s="192"/>
+      <c r="C29" s="192"/>
+      <c r="D29" s="192"/>
+      <c r="E29" s="192"/>
+      <c r="F29" s="192"/>
+      <c r="G29" s="192"/>
+      <c r="H29" s="192"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="154" t="s">
@@ -4792,16 +4792,16 @@
       </c>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="221" t="s">
+      <c r="A34" s="192" t="s">
         <v>113</v>
       </c>
-      <c r="B34" s="221"/>
-      <c r="C34" s="221"/>
-      <c r="D34" s="221"/>
-      <c r="E34" s="221"/>
-      <c r="F34" s="221"/>
-      <c r="G34" s="221"/>
-      <c r="H34" s="221"/>
+      <c r="B34" s="192"/>
+      <c r="C34" s="192"/>
+      <c r="D34" s="192"/>
+      <c r="E34" s="192"/>
+      <c r="F34" s="192"/>
+      <c r="G34" s="192"/>
+      <c r="H34" s="192"/>
     </row>
     <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="85"/>
@@ -4843,15 +4843,15 @@
       <c r="J37" s="87"/>
     </row>
     <row r="38" spans="1:10" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="180" t="s">
+      <c r="A38" s="209" t="s">
         <v>177</v>
       </c>
-      <c r="B38" s="181"/>
-      <c r="C38" s="181"/>
-      <c r="D38" s="181"/>
-      <c r="E38" s="181"/>
-      <c r="F38" s="181"/>
-      <c r="G38" s="182"/>
+      <c r="B38" s="210"/>
+      <c r="C38" s="210"/>
+      <c r="D38" s="210"/>
+      <c r="E38" s="210"/>
+      <c r="F38" s="210"/>
+      <c r="G38" s="211"/>
       <c r="H38" s="82">
         <v>-58000</v>
       </c>
@@ -4870,23 +4870,23 @@
         <v>53150</v>
       </c>
       <c r="I39" s="149"/>
-      <c r="J39" s="183"/>
+      <c r="J39" s="212"/>
     </row>
     <row r="40" spans="1:10" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="180" t="s">
+      <c r="A40" s="209" t="s">
         <v>174</v>
       </c>
-      <c r="B40" s="181"/>
-      <c r="C40" s="181"/>
-      <c r="D40" s="181"/>
-      <c r="E40" s="181"/>
-      <c r="F40" s="181"/>
-      <c r="G40" s="182"/>
+      <c r="B40" s="210"/>
+      <c r="C40" s="210"/>
+      <c r="D40" s="210"/>
+      <c r="E40" s="210"/>
+      <c r="F40" s="210"/>
+      <c r="G40" s="211"/>
       <c r="H40" s="82">
         <f>500000+245000</f>
         <v>745000</v>
       </c>
-      <c r="J40" s="183"/>
+      <c r="J40" s="212"/>
     </row>
     <row r="41" spans="1:10" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="96" t="s">
@@ -4901,7 +4901,7 @@
       <c r="H41" s="82">
         <v>500000</v>
       </c>
-      <c r="J41" s="183"/>
+      <c r="J41" s="212"/>
     </row>
     <row r="42" spans="1:10" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="96" t="s">
@@ -4916,7 +4916,7 @@
       <c r="H42" s="82">
         <v>1200000</v>
       </c>
-      <c r="J42" s="183"/>
+      <c r="J42" s="212"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="85" t="s">
@@ -4931,7 +4931,7 @@
       <c r="H43" s="82">
         <v>160000</v>
       </c>
-      <c r="J43" s="183"/>
+      <c r="J43" s="212"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="85" t="s">
@@ -4979,16 +4979,16 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="221" t="s">
+      <c r="A47" s="192" t="s">
         <v>114</v>
       </c>
-      <c r="B47" s="221"/>
-      <c r="C47" s="221"/>
-      <c r="D47" s="221"/>
-      <c r="E47" s="221"/>
-      <c r="F47" s="221"/>
-      <c r="G47" s="221"/>
-      <c r="H47" s="221"/>
+      <c r="B47" s="192"/>
+      <c r="C47" s="192"/>
+      <c r="D47" s="192"/>
+      <c r="E47" s="192"/>
+      <c r="F47" s="192"/>
+      <c r="G47" s="192"/>
+      <c r="H47" s="192"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="154" t="s">
@@ -5014,8 +5014,8 @@
         <v>147</v>
       </c>
       <c r="B49" s="154"/>
-      <c r="C49" s="201"/>
-      <c r="D49" s="202"/>
+      <c r="C49" s="230"/>
+      <c r="D49" s="231"/>
       <c r="E49" s="165"/>
       <c r="F49" s="158"/>
       <c r="G49" s="154"/>
@@ -5049,16 +5049,16 @@
       </c>
     </row>
     <row r="52" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="232" t="s">
+      <c r="A52" s="203" t="s">
         <v>116</v>
       </c>
-      <c r="B52" s="233"/>
-      <c r="C52" s="233"/>
-      <c r="D52" s="233"/>
-      <c r="E52" s="233"/>
-      <c r="F52" s="233"/>
-      <c r="G52" s="233"/>
-      <c r="H52" s="234"/>
+      <c r="B52" s="204"/>
+      <c r="C52" s="204"/>
+      <c r="D52" s="204"/>
+      <c r="E52" s="204"/>
+      <c r="F52" s="204"/>
+      <c r="G52" s="204"/>
+      <c r="H52" s="205"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="154" t="s">
@@ -5100,16 +5100,16 @@
       </c>
     </row>
     <row r="56" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="232" t="s">
+      <c r="A56" s="203" t="s">
         <v>118</v>
       </c>
-      <c r="B56" s="233"/>
-      <c r="C56" s="233"/>
-      <c r="D56" s="233"/>
-      <c r="E56" s="233"/>
-      <c r="F56" s="233"/>
-      <c r="G56" s="233"/>
-      <c r="H56" s="234"/>
+      <c r="B56" s="204"/>
+      <c r="C56" s="204"/>
+      <c r="D56" s="204"/>
+      <c r="E56" s="204"/>
+      <c r="F56" s="204"/>
+      <c r="G56" s="204"/>
+      <c r="H56" s="205"/>
       <c r="I56" s="87"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -5160,16 +5160,16 @@
       <c r="K59" s="83"/>
     </row>
     <row r="60" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="203" t="s">
+      <c r="A60" s="206" t="s">
         <v>119</v>
       </c>
-      <c r="B60" s="204"/>
-      <c r="C60" s="204"/>
-      <c r="D60" s="204"/>
-      <c r="E60" s="204"/>
-      <c r="F60" s="204"/>
-      <c r="G60" s="204"/>
-      <c r="H60" s="235"/>
+      <c r="B60" s="207"/>
+      <c r="C60" s="207"/>
+      <c r="D60" s="207"/>
+      <c r="E60" s="207"/>
+      <c r="F60" s="207"/>
+      <c r="G60" s="207"/>
+      <c r="H60" s="208"/>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="86"/>
@@ -5224,15 +5224,15 @@
       <c r="H65" s="92"/>
     </row>
     <row r="66" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="203" t="s">
+      <c r="A66" s="206" t="s">
         <v>152</v>
       </c>
-      <c r="B66" s="204"/>
-      <c r="C66" s="204"/>
-      <c r="D66" s="204"/>
-      <c r="E66" s="204"/>
-      <c r="F66" s="204"/>
-      <c r="G66" s="204"/>
+      <c r="B66" s="207"/>
+      <c r="C66" s="207"/>
+      <c r="D66" s="207"/>
+      <c r="E66" s="207"/>
+      <c r="F66" s="207"/>
+      <c r="G66" s="207"/>
       <c r="H66" s="128"/>
     </row>
     <row r="67" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5281,25 +5281,25 @@
       <c r="H70" s="92"/>
     </row>
     <row r="71" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A71" s="195" t="s">
+      <c r="A71" s="224" t="s">
         <v>120</v>
       </c>
-      <c r="B71" s="195"/>
-      <c r="C71" s="195"/>
-      <c r="D71" s="195"/>
-      <c r="E71" s="195"/>
-      <c r="F71" s="195"/>
-      <c r="G71" s="195"/>
+      <c r="B71" s="224"/>
+      <c r="C71" s="224"/>
+      <c r="D71" s="224"/>
+      <c r="E71" s="224"/>
+      <c r="F71" s="224"/>
+      <c r="G71" s="224"/>
       <c r="H71" s="95"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="180"/>
-      <c r="B72" s="181"/>
-      <c r="C72" s="181"/>
-      <c r="D72" s="181"/>
-      <c r="E72" s="181"/>
-      <c r="F72" s="181"/>
-      <c r="G72" s="182"/>
+      <c r="A72" s="209"/>
+      <c r="B72" s="210"/>
+      <c r="C72" s="210"/>
+      <c r="D72" s="210"/>
+      <c r="E72" s="210"/>
+      <c r="F72" s="210"/>
+      <c r="G72" s="211"/>
       <c r="H72" s="124"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
@@ -5313,13 +5313,13 @@
       <c r="H73" s="124"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="196"/>
-      <c r="B74" s="197"/>
-      <c r="C74" s="197"/>
-      <c r="D74" s="197"/>
-      <c r="E74" s="197"/>
-      <c r="F74" s="197"/>
-      <c r="G74" s="198"/>
+      <c r="A74" s="225"/>
+      <c r="B74" s="226"/>
+      <c r="C74" s="226"/>
+      <c r="D74" s="226"/>
+      <c r="E74" s="226"/>
+      <c r="F74" s="226"/>
+      <c r="G74" s="227"/>
       <c r="H74" s="82">
         <v>0</v>
       </c>
@@ -5375,15 +5375,15 @@
       <c r="I78" s="87"/>
     </row>
     <row r="79" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="199" t="s">
+      <c r="A79" s="228" t="s">
         <v>121</v>
       </c>
-      <c r="B79" s="200"/>
-      <c r="C79" s="200"/>
-      <c r="D79" s="200"/>
-      <c r="E79" s="200"/>
-      <c r="F79" s="200"/>
-      <c r="G79" s="200"/>
+      <c r="B79" s="229"/>
+      <c r="C79" s="229"/>
+      <c r="D79" s="229"/>
+      <c r="E79" s="229"/>
+      <c r="F79" s="229"/>
+      <c r="G79" s="229"/>
       <c r="H79" s="140">
         <f>H77</f>
         <v>0</v>
@@ -5391,42 +5391,42 @@
       <c r="I79" s="87"/>
     </row>
     <row r="80" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="192" t="s">
+      <c r="A80" s="221" t="s">
         <v>122</v>
       </c>
-      <c r="B80" s="193"/>
-      <c r="C80" s="193"/>
-      <c r="D80" s="193"/>
-      <c r="E80" s="193"/>
-      <c r="F80" s="193"/>
-      <c r="G80" s="194"/>
+      <c r="B80" s="222"/>
+      <c r="C80" s="222"/>
+      <c r="D80" s="222"/>
+      <c r="E80" s="222"/>
+      <c r="F80" s="222"/>
+      <c r="G80" s="223"/>
       <c r="H80" s="140"/>
       <c r="I80" s="88"/>
     </row>
     <row r="81" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="205" t="s">
+      <c r="A81" s="232" t="s">
         <v>142</v>
       </c>
-      <c r="B81" s="206"/>
-      <c r="C81" s="206"/>
-      <c r="D81" s="206"/>
-      <c r="E81" s="206"/>
-      <c r="F81" s="206"/>
-      <c r="G81" s="207"/>
+      <c r="B81" s="233"/>
+      <c r="C81" s="233"/>
+      <c r="D81" s="233"/>
+      <c r="E81" s="233"/>
+      <c r="F81" s="233"/>
+      <c r="G81" s="234"/>
       <c r="H81" s="140"/>
       <c r="I81" s="87"/>
       <c r="J81" s="83"/>
     </row>
     <row r="82" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A82" s="199" t="s">
+      <c r="A82" s="228" t="s">
         <v>123</v>
       </c>
-      <c r="B82" s="200"/>
-      <c r="C82" s="200"/>
-      <c r="D82" s="200"/>
-      <c r="E82" s="200"/>
-      <c r="F82" s="200"/>
-      <c r="G82" s="200"/>
+      <c r="B82" s="229"/>
+      <c r="C82" s="229"/>
+      <c r="D82" s="229"/>
+      <c r="E82" s="229"/>
+      <c r="F82" s="229"/>
+      <c r="G82" s="229"/>
       <c r="H82" s="140">
         <f>H63+H59+H55+H51+H46+H33+H16+H21+H28+H69</f>
         <v>6696913.4500000002</v>
@@ -5434,15 +5434,15 @@
       <c r="I82" s="83"/>
     </row>
     <row r="83" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A83" s="208" t="s">
+      <c r="A83" s="235" t="s">
         <v>124</v>
       </c>
-      <c r="B83" s="209"/>
-      <c r="C83" s="209"/>
-      <c r="D83" s="209"/>
-      <c r="E83" s="209"/>
-      <c r="F83" s="209"/>
-      <c r="G83" s="210"/>
+      <c r="B83" s="236"/>
+      <c r="C83" s="236"/>
+      <c r="D83" s="236"/>
+      <c r="E83" s="236"/>
+      <c r="F83" s="236"/>
+      <c r="G83" s="237"/>
       <c r="H83" s="141">
         <f>H82+H80</f>
         <v>6696913.4500000002</v>
@@ -5451,15 +5451,15 @@
       <c r="K83" s="149"/>
     </row>
     <row r="84" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A84" s="208" t="s">
+      <c r="A84" s="235" t="s">
         <v>125</v>
       </c>
-      <c r="B84" s="209"/>
-      <c r="C84" s="209"/>
-      <c r="D84" s="209"/>
-      <c r="E84" s="209"/>
-      <c r="F84" s="209"/>
-      <c r="G84" s="210"/>
+      <c r="B84" s="236"/>
+      <c r="C84" s="236"/>
+      <c r="D84" s="236"/>
+      <c r="E84" s="236"/>
+      <c r="F84" s="236"/>
+      <c r="G84" s="237"/>
       <c r="H84" s="142">
         <f>H79+H81</f>
         <v>0</v>
@@ -5467,30 +5467,30 @@
       <c r="I84" s="83"/>
     </row>
     <row r="85" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="211" t="s">
+      <c r="A85" s="182" t="s">
         <v>126</v>
       </c>
-      <c r="B85" s="212"/>
-      <c r="C85" s="212"/>
-      <c r="D85" s="212"/>
-      <c r="E85" s="212"/>
-      <c r="F85" s="212"/>
-      <c r="G85" s="212"/>
+      <c r="B85" s="183"/>
+      <c r="C85" s="183"/>
+      <c r="D85" s="183"/>
+      <c r="E85" s="183"/>
+      <c r="F85" s="183"/>
+      <c r="G85" s="183"/>
       <c r="H85" s="143">
         <f>H82+H79</f>
         <v>6696913.4500000002</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="213" t="s">
+      <c r="A86" s="184" t="s">
         <v>127</v>
       </c>
-      <c r="B86" s="214"/>
-      <c r="C86" s="214"/>
-      <c r="D86" s="214"/>
-      <c r="E86" s="214"/>
-      <c r="F86" s="214"/>
-      <c r="G86" s="214"/>
+      <c r="B86" s="185"/>
+      <c r="C86" s="185"/>
+      <c r="D86" s="185"/>
+      <c r="E86" s="185"/>
+      <c r="F86" s="185"/>
+      <c r="G86" s="185"/>
       <c r="H86" s="100">
         <v>0</v>
       </c>
@@ -5506,26 +5506,26 @@
       <c r="H87" s="102"/>
     </row>
     <row r="88" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="215" t="s">
+      <c r="A88" s="186" t="s">
         <v>161</v>
       </c>
-      <c r="B88" s="216"/>
-      <c r="C88" s="216"/>
-      <c r="D88" s="216"/>
-      <c r="E88" s="216"/>
-      <c r="F88" s="216"/>
-      <c r="G88" s="216"/>
-      <c r="H88" s="217"/>
+      <c r="B88" s="187"/>
+      <c r="C88" s="187"/>
+      <c r="D88" s="187"/>
+      <c r="E88" s="187"/>
+      <c r="F88" s="187"/>
+      <c r="G88" s="187"/>
+      <c r="H88" s="188"/>
     </row>
     <row r="89" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="218"/>
-      <c r="B89" s="219"/>
-      <c r="C89" s="219"/>
-      <c r="D89" s="219"/>
-      <c r="E89" s="219"/>
-      <c r="F89" s="219"/>
-      <c r="G89" s="219"/>
-      <c r="H89" s="220"/>
+      <c r="A89" s="189"/>
+      <c r="B89" s="190"/>
+      <c r="C89" s="190"/>
+      <c r="D89" s="190"/>
+      <c r="E89" s="190"/>
+      <c r="F89" s="190"/>
+      <c r="G89" s="190"/>
+      <c r="H89" s="191"/>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="6"/>
@@ -5538,16 +5538,16 @@
       <c r="H90" s="6"/>
     </row>
     <row r="91" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A91" s="184" t="s">
+      <c r="A91" s="213" t="s">
         <v>128</v>
       </c>
-      <c r="B91" s="185"/>
-      <c r="C91" s="185"/>
-      <c r="D91" s="185"/>
-      <c r="E91" s="185"/>
-      <c r="F91" s="185"/>
-      <c r="G91" s="185"/>
-      <c r="H91" s="186"/>
+      <c r="B91" s="214"/>
+      <c r="C91" s="214"/>
+      <c r="D91" s="214"/>
+      <c r="E91" s="214"/>
+      <c r="F91" s="214"/>
+      <c r="G91" s="214"/>
+      <c r="H91" s="215"/>
     </row>
     <row r="92" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A92" s="103" t="s">
@@ -5640,16 +5640,16 @@
     </row>
     <row r="98" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="99" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="187" t="s">
+      <c r="A99" s="216" t="s">
         <v>133</v>
       </c>
-      <c r="B99" s="188"/>
-      <c r="C99" s="188"/>
-      <c r="D99" s="188"/>
-      <c r="E99" s="188"/>
-      <c r="F99" s="188"/>
-      <c r="G99" s="188"/>
-      <c r="H99" s="189"/>
+      <c r="B99" s="217"/>
+      <c r="C99" s="217"/>
+      <c r="D99" s="217"/>
+      <c r="E99" s="217"/>
+      <c r="F99" s="217"/>
+      <c r="G99" s="217"/>
+      <c r="H99" s="218"/>
     </row>
     <row r="100" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="113" t="s">
@@ -5777,14 +5777,30 @@
         <v>100</v>
       </c>
       <c r="B116" s="120"/>
-      <c r="C116" s="190">
+      <c r="C116" s="219">
         <f>SUM(D112:D115)</f>
         <v>0</v>
       </c>
-      <c r="D116" s="191"/>
+      <c r="D116" s="220"/>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="J39:J43"/>
+    <mergeCell ref="A91:H91"/>
+    <mergeCell ref="A99:H99"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="A80:G80"/>
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A72:G72"/>
+    <mergeCell ref="A74:G74"/>
+    <mergeCell ref="A79:G79"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="A66:G66"/>
+    <mergeCell ref="A81:G81"/>
+    <mergeCell ref="A82:G82"/>
+    <mergeCell ref="A83:G83"/>
+    <mergeCell ref="A84:G84"/>
     <mergeCell ref="A85:G85"/>
     <mergeCell ref="A86:G86"/>
     <mergeCell ref="A88:H89"/>
@@ -5801,22 +5817,6 @@
     <mergeCell ref="A56:H56"/>
     <mergeCell ref="A60:H60"/>
     <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="J39:J43"/>
-    <mergeCell ref="A91:H91"/>
-    <mergeCell ref="A99:H99"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="A80:G80"/>
-    <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A72:G72"/>
-    <mergeCell ref="A74:G74"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="A66:G66"/>
-    <mergeCell ref="A81:G81"/>
-    <mergeCell ref="A82:G82"/>
-    <mergeCell ref="A83:G83"/>
-    <mergeCell ref="A84:G84"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
